--- a/bom/ULX4M-LS-V004-BOM.xlsx
+++ b/bom/ULX4M-LS-V004-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="358">
   <si>
     <t xml:space="preserve">Reference</t>
   </si>
@@ -454,31 +454,16 @@
     <t xml:space="preserve">L1, L2, L3</t>
   </si>
   <si>
-    <t xml:space="preserve">BLM21SP181SH1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferrite Beads Multi-Layer Power 180Ohm 25% 100MHz 4A 0.02Ohm DCR 0805 T/R Automotive AEC-Q200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mouser 81-BLM21SP181SH1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/opatz8j6/a1?t=R-F6qeNetvun7KL4Qr-DAIpuFJsE2n-RWXVWIhyvjPS4kudBsSNxn29-PvHEpq-gBLpzX03i2fKlhnnt-E95cBkDjN2nw4pHSQoEqhhIhUuP0eNLQ4MRiKDm-srVqQ-drb8kai52UYuIP5qnjkUfztIC3DZDIHzOjXhi55c1kwHhRwjM_62gRwZ4WUPdr_IEp66KbwTolG7cu_AC5yTyM-U6gqgm8-wGGFcYKE4KBSfTHDqTFbQNkZsct7CWQfceWO_-iOM0np7_bYbZZ8MZ5tuKWZPq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TME BLM21SP181SH1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/opatz8j6/a1?t=GEL-4EyCMzN5rSY2rHtMak9amUVWNUpd6nsaOdGsLWeUdmdLEQogjKqlp6y9UgkBejei4Nxoo73rRSa6fDTD1AxPpe-nu_QFLC2yDBWfBzaUvZoz5vw-PZPQa_TzSnDBeQGSXWbs_Tkms6Qs3KLzErCK4v-bJVO9un-r2q-S6Dt7Zs-wsc5hfGHtc5zmmL5euaYGC8n4Oc1YEX6Yqwx4j2L1UJZlVNqc03BcfYRbgjx8N5FsGkZg_b5tt4iwFYjEVw6v_Irbh33rf5SmB-b357o0XHnh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">490-18585-1-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81-BLM21SP181SH1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65AC5848</t>
+    <t xml:space="preserve">DFE322520F-2R2M=P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductor Chip Shielded Wirewound 2.2uH 20% 1MHz Metal Alloy 3.3A 1210 Emboss T/R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81-DFE322520F2R2M=P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://octopart.com/opatz8j6/a1?t=9Cr7-k-NMVDZL2fACYvcAPvm9HA_Q8ESxvMDcPYvTe7GJyBvhUiDs6C-skCNCkMi63DmLZhhkxkE-dEqm_fdj3jtlD-jNPF9BxH1OJ-zdGqd3fabyJi4hBIAOSMg524GzfPY4G1o8Ya2GTJHk7zklVDaQ7U-jKySVu4BWjHmE-8jSHl4nKoXDv6ordOtAZDH-m4J4GduFr9hVR436w-o4R9_k3jLTaOT66tB1z63o_Ozv2k55R38Ssof8Bzo-XyMgF0TMGioVITBKcnOvEbW2JFicCebEQ</t>
   </si>
   <si>
     <t xml:space="preserve">U5, U6, U7</t>
@@ -1123,11 +1108,12 @@
     <numFmt numFmtId="168" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1153,17 +1139,23 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1213,30 +1205,52 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="25" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="25" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1497,2738 +1511,2700 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB38"/>
-  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="67.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="125.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="73.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="125.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="12.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="30.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="73.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="125.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="38.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="41.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="55.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="38.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="41.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="63.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="20.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="22.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="18.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="49.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="67.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="125.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="73.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="125.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="73.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="125.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="38.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="41.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="55.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="38.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="41.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="18.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="63.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="22.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="18.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="12.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0" t="n">
+      <c r="J2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.0403</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="W2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="0" t="s">
+      <c r="X2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="0" t="s">
+      <c r="Y2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" s="0" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.00118</v>
       </c>
-      <c r="AA2" s="0" t="n">
+      <c r="AA2" s="1" t="n">
         <v>0.43701</v>
       </c>
-      <c r="AB2" s="0" t="n">
+      <c r="AB2" s="1" t="n">
         <v>369</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="n">
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.189</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="N3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="0" t="s">
+      <c r="R3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="0" t="s">
+      <c r="W3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="0" t="s">
+      <c r="X3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z3" s="0" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="AA3" s="0" t="n">
+      <c r="AA3" s="1" t="n">
         <v>9.87</v>
       </c>
-      <c r="AB3" s="0" t="n">
+      <c r="AB3" s="1" t="n">
         <v>16172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0" t="n">
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.21</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="N4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P4" s="0" t="s">
+      <c r="P4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="0" t="s">
+      <c r="R4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W4" s="0" t="s">
+      <c r="W4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="0" t="s">
+      <c r="X4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z4" s="0" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.00783</v>
       </c>
-      <c r="AA4" s="0" t="n">
+      <c r="AA4" s="1" t="n">
         <v>16.45</v>
       </c>
-      <c r="AB4" s="0" t="n">
+      <c r="AB4" s="1" t="n">
         <v>41966</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0" t="n">
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.24</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="W5" s="0" t="s">
+      <c r="W5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X5" s="0" t="s">
+      <c r="X5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z5" s="0" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.00729</v>
       </c>
-      <c r="AA5" s="0" t="n">
+      <c r="AA5" s="1" t="n">
         <v>12.39</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="AB5" s="1" t="n">
         <v>9990</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0" t="n">
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>1.35</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="R6" s="0" t="s">
+      <c r="R6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="W6" s="0" t="s">
+      <c r="W6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="X6" s="0" t="s">
+      <c r="X6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z6" s="0" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.03944</v>
       </c>
-      <c r="AA6" s="0" t="n">
+      <c r="AA6" s="1" t="n">
         <v>43.38</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="AB6" s="1" t="n">
         <v>30510</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="n">
+      <c r="J7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.91</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="N7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="0" t="s">
+      <c r="P7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="Q7" s="0" t="s">
+      <c r="Q7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="R7" s="0" t="s">
+      <c r="R7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="U7" s="0" t="s">
+      <c r="U7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>2478053</v>
       </c>
-      <c r="W7" s="0" t="s">
+      <c r="W7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X7" s="0" t="s">
+      <c r="X7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z7" s="0" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.0129</v>
       </c>
-      <c r="AA7" s="0" t="n">
+      <c r="AA7" s="1" t="n">
         <v>15.48</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="AB7" s="1" t="n">
         <v>6180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="n">
+      <c r="J8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="N8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="P8" s="0" t="s">
+      <c r="P8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Q8" s="0" t="s">
+      <c r="Q8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="R8" s="0" t="s">
+      <c r="R8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="U8" s="0" t="s">
+      <c r="U8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>1978008</v>
       </c>
-      <c r="W8" s="0" t="s">
+      <c r="W8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X8" s="0" t="s">
+      <c r="X8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="Z8" s="1" t="n">
         <v>0.00456</v>
       </c>
-      <c r="AA8" s="0" t="n">
+      <c r="AA8" s="1" t="n">
         <v>4.56</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="AB8" s="1" t="n">
         <v>8750</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="n">
+      <c r="J9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.079</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="N9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="P9" s="0" t="s">
+      <c r="P9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" s="0" t="s">
+      <c r="Q9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="R9" s="0" t="s">
+      <c r="R9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>5139968</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="U9" s="0" t="s">
+      <c r="U9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="W9" s="0" t="s">
+      <c r="W9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X9" s="0" t="s">
+      <c r="X9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z9" s="0" t="n">
+      <c r="Z9" s="1" t="n">
         <v>0.00683</v>
       </c>
-      <c r="AA9" s="0" t="n">
+      <c r="AA9" s="1" t="n">
         <v>4.1</v>
       </c>
-      <c r="AB9" s="0" t="n">
+      <c r="AB9" s="1" t="n">
         <v>29893</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="0" t="n">
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.07</v>
       </c>
-      <c r="N10" s="0" t="s">
+      <c r="N10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="Q10" s="0" t="s">
+      <c r="Q10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="R10" s="0" t="s">
+      <c r="R10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="U10" s="0" t="s">
+      <c r="U10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="0" t="s">
+      <c r="W10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X10" s="0" t="s">
+      <c r="X10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y10" s="0" t="s">
+      <c r="Y10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z10" s="0" t="n">
+      <c r="Z10" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="AA10" s="0" t="n">
+      <c r="AA10" s="1" t="n">
         <v>1.12</v>
       </c>
-      <c r="AB10" s="0" t="n">
+      <c r="AB10" s="1" t="n">
         <v>52516</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="0" t="n">
+      <c r="J11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.138</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="N11" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="P11" s="0" t="s">
+      <c r="P11" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Q11" s="0" t="s">
+      <c r="Q11" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="R11" s="0" t="s">
+      <c r="R11" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="1" t="n">
         <v>4190584</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="U11" s="0" t="s">
+      <c r="U11" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="W11" s="0" t="s">
+      <c r="W11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X11" s="0" t="s">
+      <c r="X11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y11" s="0" t="s">
+      <c r="Y11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z11" s="0" t="n">
+      <c r="Z11" s="1" t="n">
         <v>0.0325</v>
       </c>
-      <c r="AA11" s="0" t="n">
+      <c r="AA11" s="1" t="n">
         <v>16.25</v>
       </c>
-      <c r="AB11" s="0" t="n">
+      <c r="AB11" s="1" t="n">
         <v>2230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I12" s="0" t="s">
+      <c r="I12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0" t="n">
+      <c r="J12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.14</v>
       </c>
-      <c r="N12" s="0" t="s">
+      <c r="N12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="R12" s="0" t="s">
+      <c r="R12" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="T12" s="0" t="s">
+      <c r="T12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="W12" s="0" t="s">
+      <c r="W12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X12" s="0" t="s">
+      <c r="X12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y12" s="0" t="s">
+      <c r="Y12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z12" s="0" t="n">
+      <c r="Z12" s="1" t="n">
         <v>0.0082</v>
       </c>
-      <c r="AA12" s="0" t="n">
+      <c r="AA12" s="1" t="n">
         <v>6.56</v>
       </c>
-      <c r="AB12" s="0" t="n">
+      <c r="AB12" s="1" t="n">
         <v>29460</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I13" s="0" t="s">
+      <c r="I13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0" t="n">
+      <c r="J13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="N13" s="0" t="s">
+      <c r="N13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="R13" s="0" t="s">
+      <c r="R13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="T13" s="0" t="s">
+      <c r="T13" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="W13" s="0" t="s">
+      <c r="W13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X13" s="0" t="s">
+      <c r="X13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y13" s="0" t="s">
+      <c r="Y13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z13" s="0" t="n">
+      <c r="Z13" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="AA13" s="0" t="n">
+      <c r="AA13" s="1" t="n">
         <v>3.05</v>
       </c>
-      <c r="AB13" s="0" t="n">
+      <c r="AB13" s="1" t="n">
         <v>10054</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="I14" s="0" t="s">
+      <c r="I14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="0" t="n">
+      <c r="J14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="0" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N14" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="R14" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="T14" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="U14" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="W14" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="X14" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y14" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z14" s="0" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AA14" s="0" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="AB14" s="0" t="n">
-        <v>1835</v>
-      </c>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="I15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="O15" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="P15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F15" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="T15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="P15" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="R15" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="T15" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="W15" s="0" t="s">
+      <c r="W15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X15" s="0" t="s">
+      <c r="X15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Z15" s="0" t="n">
+      <c r="Z15" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="AA15" s="0" t="n">
+      <c r="AA15" s="1" t="n">
         <v>38.11</v>
       </c>
-      <c r="AB15" s="0" t="n">
+      <c r="AB15" s="1" t="n">
         <v>12574</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="I16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="O16" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="U16" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" s="0" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="N16" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="U16" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="W16" s="0" t="s">
+      <c r="W16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X16" s="0" t="s">
+      <c r="X16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y16" s="0" t="s">
+      <c r="Y16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z16" s="0" t="n">
+      <c r="Z16" s="1" t="n">
         <v>0.36805</v>
       </c>
-      <c r="AA16" s="0" t="n">
+      <c r="AA16" s="1" t="n">
         <v>110.41</v>
       </c>
-      <c r="AB16" s="0" t="n">
+      <c r="AB16" s="1" t="n">
         <v>422</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="I17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="Q17" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="T17" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="0" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N17" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q17" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="T17" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="W17" s="0" t="s">
+      <c r="W17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X17" s="0" t="s">
+      <c r="X17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y17" s="0" t="s">
+      <c r="Y17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z17" s="0" t="n">
+      <c r="Z17" s="1" t="n">
         <v>0.06468</v>
       </c>
-      <c r="AA17" s="0" t="n">
+      <c r="AA17" s="1" t="n">
         <v>25.87</v>
       </c>
-      <c r="AB17" s="0" t="n">
+      <c r="AB17" s="1" t="n">
         <v>25210</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="I18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="P18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" s="0" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="N18" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="P18" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q18" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="R18" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="S18" s="0" t="n">
+      <c r="S18" s="1" t="n">
         <v>5050042</v>
       </c>
-      <c r="V18" s="0" t="n">
+      <c r="V18" s="1" t="n">
         <v>6920981</v>
       </c>
-      <c r="W18" s="0" t="s">
+      <c r="W18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X18" s="0" t="s">
+      <c r="X18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y18" s="0" t="s">
+      <c r="Y18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z18" s="0" t="n">
+      <c r="Z18" s="1" t="n">
         <v>0.05912</v>
       </c>
-      <c r="AA18" s="0" t="n">
+      <c r="AA18" s="1" t="n">
         <v>11.82</v>
       </c>
-      <c r="AB18" s="0" t="n">
+      <c r="AB18" s="1" t="n">
         <v>12041</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="O19" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="R19" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I19" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="0" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N19" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="R19" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="S19" s="0" t="n">
+      <c r="S19" s="1" t="n">
         <v>4438875</v>
       </c>
-      <c r="V19" s="0" t="n">
+      <c r="V19" s="1" t="n">
         <v>6920994</v>
       </c>
-      <c r="W19" s="0" t="s">
+      <c r="W19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X19" s="0" t="s">
+      <c r="X19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y19" s="0" t="s">
+      <c r="Y19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z19" s="0" t="n">
+      <c r="Z19" s="1" t="n">
         <v>0.0734</v>
       </c>
-      <c r="AA19" s="0" t="n">
+      <c r="AA19" s="1" t="n">
         <v>14.68</v>
       </c>
-      <c r="AB19" s="0" t="n">
+      <c r="AB19" s="1" t="n">
         <v>18883</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="P20" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="I20" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N20" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="P20" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="R20" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="W20" s="0" t="s">
+      <c r="W20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X20" s="0" t="s">
+      <c r="X20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y20" s="0" t="s">
+      <c r="Y20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z20" s="0" t="n">
+      <c r="Z20" s="1" t="n">
         <v>0.125</v>
       </c>
-      <c r="AA20" s="0" t="n">
+      <c r="AA20" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AB20" s="0" t="n">
+      <c r="AB20" s="1" t="n">
         <v>47325</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="O21" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="P21" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F21" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I21" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N21" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="P21" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="R21" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="S21" s="0" t="n">
+      <c r="S21" s="1" t="n">
         <v>3023739</v>
       </c>
-      <c r="V21" s="0" t="n">
+      <c r="V21" s="1" t="n">
         <v>6921010</v>
       </c>
-      <c r="W21" s="0" t="s">
+      <c r="W21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X21" s="0" t="s">
+      <c r="X21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y21" s="0" t="s">
+      <c r="Y21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z21" s="0" t="n">
+      <c r="Z21" s="1" t="n">
         <v>0.0433</v>
       </c>
-      <c r="AA21" s="0" t="n">
+      <c r="AA21" s="1" t="n">
         <v>8.66</v>
       </c>
-      <c r="AB21" s="0" t="n">
+      <c r="AB21" s="1" t="n">
         <v>6081</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="I22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="P22" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="T22" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F22" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I22" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" s="0" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N22" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="P22" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="R22" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="T22" s="0" t="s">
-        <v>220</v>
-      </c>
-      <c r="W22" s="0" t="s">
+      <c r="W22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X22" s="0" t="s">
+      <c r="X22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y22" s="0" t="s">
+      <c r="Y22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z22" s="0" t="n">
+      <c r="Z22" s="1" t="n">
         <v>0.06924</v>
       </c>
-      <c r="AA22" s="0" t="n">
+      <c r="AA22" s="1" t="n">
         <v>13.85</v>
       </c>
-      <c r="AB22" s="0" t="n">
+      <c r="AB22" s="1" t="n">
         <v>1313</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="I23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="P23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="0" t="s">
+      <c r="T23" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="U23" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I23" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="0" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="N23" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="P23" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q23" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="R23" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="T23" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="U23" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="W23" s="0" t="s">
+      <c r="W23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X23" s="0" t="s">
+      <c r="X23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y23" s="0" t="s">
+      <c r="Y23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z23" s="0" t="n">
+      <c r="Z23" s="1" t="n">
         <v>0.61857</v>
       </c>
-      <c r="AA23" s="0" t="n">
+      <c r="AA23" s="1" t="n">
         <v>123.71</v>
       </c>
-      <c r="AB23" s="0" t="n">
+      <c r="AB23" s="1" t="n">
         <v>2724</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="I24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="O24" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="Q24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F24" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="T24" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="0" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N24" s="0" t="s">
-        <v>237</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q24" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="R24" s="0" t="s">
-        <v>239</v>
-      </c>
-      <c r="T24" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="W24" s="0" t="s">
+      <c r="W24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X24" s="0" t="s">
+      <c r="X24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y24" s="0" t="s">
+      <c r="Y24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z24" s="0" t="n">
+      <c r="Z24" s="1" t="n">
         <v>1.07</v>
       </c>
-      <c r="AA24" s="0" t="n">
+      <c r="AA24" s="1" t="n">
         <v>214</v>
       </c>
-      <c r="AB24" s="0" t="n">
+      <c r="AB24" s="1" t="n">
         <v>2183</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="O25" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="P25" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F25" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="T25" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="U25" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="I25" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="K25" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N25" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="P25" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="R25" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="T25" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="U25" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="W25" s="0" t="s">
+      <c r="W25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="X25" s="0" t="s">
+      <c r="X25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y25" s="0" t="s">
+      <c r="Y25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z25" s="0" t="n">
+      <c r="Z25" s="1" t="n">
         <v>0.00802</v>
       </c>
-      <c r="AA25" s="0" t="n">
+      <c r="AA25" s="1" t="n">
         <v>11.23</v>
       </c>
-      <c r="AB25" s="0" t="n">
+      <c r="AB25" s="1" t="n">
         <v>58257</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="F26" s="0" t="n">
+      <c r="I26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.192</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="J27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="O27" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="P27" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="R27" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="T27" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="0" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="N27" s="0" t="s">
-        <v>263</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="P27" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="R27" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="T27" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="W27" s="0" t="s">
+      <c r="W27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X27" s="0" t="s">
+      <c r="X27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y27" s="0" t="s">
+      <c r="Y27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z27" s="0" t="n">
+      <c r="Z27" s="1" t="n">
         <v>79.7</v>
       </c>
-      <c r="AA27" s="0" t="n">
+      <c r="AA27" s="1" t="n">
         <v>7970.38</v>
       </c>
-      <c r="AB27" s="0" t="n">
+      <c r="AB27" s="1" t="n">
         <v>208</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="I28" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="J28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="O28" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="F28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="Q28" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="T28" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="I28" s="0" t="s">
+      <c r="U28" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="0" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="N28" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q28" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="T28" s="0" t="s">
-        <v>278</v>
-      </c>
-      <c r="U28" s="0" t="s">
-        <v>279</v>
-      </c>
-      <c r="W28" s="0" t="s">
+      <c r="W28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X28" s="0" t="s">
+      <c r="X28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y28" s="0" t="s">
+      <c r="Y28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z28" s="0" t="n">
+      <c r="Z28" s="1" t="n">
         <v>21.86</v>
       </c>
-      <c r="AA28" s="0" t="n">
+      <c r="AA28" s="1" t="n">
         <v>2185.5</v>
       </c>
-      <c r="AB28" s="0" t="n">
+      <c r="AB28" s="1" t="n">
         <v>792</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="O29" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="P29" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>270</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="T29" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="0" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="N29" s="0" t="s">
-        <v>283</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="P29" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q29" s="0" t="s">
-        <v>286</v>
-      </c>
-      <c r="T29" s="0" t="s">
-        <v>287</v>
-      </c>
-      <c r="W29" s="0" t="s">
+      <c r="W29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X29" s="0" t="s">
+      <c r="X29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y29" s="0" t="s">
+      <c r="Y29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z29" s="0" t="n">
+      <c r="Z29" s="1" t="n">
         <v>1.47</v>
       </c>
-      <c r="AA29" s="0" t="n">
+      <c r="AA29" s="1" t="n">
         <v>146.85</v>
       </c>
-      <c r="AB29" s="0" t="n">
+      <c r="AB29" s="1" t="n">
         <v>3240</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="I30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="O30" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="P30" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="R30" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="S30" s="1" t="n">
+        <v>7025411</v>
+      </c>
+      <c r="T30" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I30" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="0" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="N30" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="P30" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="R30" s="0" t="s">
-        <v>297</v>
-      </c>
-      <c r="S30" s="0" t="n">
-        <v>7025411</v>
-      </c>
-      <c r="T30" s="0" t="s">
-        <v>298</v>
-      </c>
-      <c r="W30" s="0" t="s">
+      <c r="W30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X30" s="0" t="s">
+      <c r="X30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Z30" s="0" t="n">
+      <c r="Z30" s="1" t="n">
         <v>3.18</v>
       </c>
-      <c r="AA30" s="0" t="n">
+      <c r="AA30" s="1" t="n">
         <v>41.36</v>
       </c>
-      <c r="AB30" s="0" t="n">
+      <c r="AB30" s="1" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="I31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O31" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="R31" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="T31" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="U31" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" s="0" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N31" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="R31" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="T31" s="0" t="s">
-        <v>307</v>
-      </c>
-      <c r="U31" s="0" t="s">
-        <v>308</v>
-      </c>
-      <c r="W31" s="0" t="s">
+      <c r="W31" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X31" s="0" t="s">
+      <c r="X31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y31" s="0" t="s">
+      <c r="Y31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z31" s="0" t="n">
+      <c r="Z31" s="1" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA31" s="0" t="n">
+      <c r="AA31" s="1" t="n">
         <v>193.13</v>
       </c>
-      <c r="AB31" s="0" t="n">
+      <c r="AB31" s="1" t="n">
         <v>359</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="J32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="O32" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="P32" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q32" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="0" t="s">
+      <c r="R32" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="T32" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="J32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" s="0" t="n">
-        <v>0.2901</v>
-      </c>
-      <c r="N32" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="P32" s="0" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q32" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="R32" s="0" t="s">
-        <v>317</v>
-      </c>
-      <c r="T32" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="U32" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="V32" s="0" t="n">
+      <c r="U32" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="V32" s="1" t="n">
         <v>1822981</v>
       </c>
-      <c r="W32" s="0" t="s">
+      <c r="W32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X32" s="0" t="s">
+      <c r="X32" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y32" s="0" t="s">
+      <c r="Y32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z32" s="0" t="n">
+      <c r="Z32" s="1" t="n">
         <v>0.19204</v>
       </c>
-      <c r="AA32" s="0" t="n">
+      <c r="AA32" s="1" t="n">
         <v>19.2</v>
       </c>
-      <c r="AB32" s="0" t="n">
+      <c r="AB32" s="1" t="n">
         <v>1093</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O33" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="P33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="0" t="s">
+      <c r="R33" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="S33" s="1" t="n">
+        <v>5110652</v>
+      </c>
+      <c r="T33" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="0" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="N33" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="P33" s="0" t="s">
+      <c r="U33" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="Q33" s="0" t="s">
-        <v>325</v>
-      </c>
-      <c r="R33" s="0" t="s">
-        <v>326</v>
-      </c>
-      <c r="S33" s="0" t="n">
-        <v>5110652</v>
-      </c>
-      <c r="T33" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="U33" s="0" t="s">
-        <v>325</v>
-      </c>
-      <c r="W33" s="0" t="s">
+      <c r="W33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X33" s="0" t="s">
+      <c r="X33" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y33" s="0" t="s">
+      <c r="Y33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z33" s="0" t="n">
+      <c r="Z33" s="1" t="n">
         <v>0.00246</v>
       </c>
-      <c r="AA33" s="0" t="n">
+      <c r="AA33" s="1" t="n">
         <v>0.24597</v>
       </c>
-      <c r="AB33" s="0" t="n">
+      <c r="AB33" s="1" t="n">
         <v>15198</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="O34" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="P34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="0" t="s">
+      <c r="T34" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="F34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="I34" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="M34" s="0" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="N34" s="0" t="s">
-        <v>331</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="P34" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="R34" s="0" t="s">
-        <v>334</v>
-      </c>
-      <c r="T34" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="W34" s="0" t="s">
+      <c r="W34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X34" s="0" t="s">
+      <c r="X34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y34" s="0" t="s">
+      <c r="Y34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z34" s="0" t="n">
+      <c r="Z34" s="1" t="n">
         <v>0.00547</v>
       </c>
-      <c r="AA34" s="0" t="n">
+      <c r="AA34" s="1" t="n">
         <v>0.5466</v>
       </c>
-      <c r="AB34" s="0" t="n">
+      <c r="AB34" s="1" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="Q35" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C35" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="0" t="s">
+      <c r="T35" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="0" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N35" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q35" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="T35" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="U35" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="W35" s="0" t="s">
+      <c r="U35" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="W35" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X35" s="0" t="s">
+      <c r="X35" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y35" s="0" t="s">
+      <c r="Y35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z35" s="0" t="n">
+      <c r="Z35" s="1" t="n">
         <v>0.00091</v>
       </c>
-      <c r="AA35" s="0" t="n">
+      <c r="AA35" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="AB35" s="0" t="n">
+      <c r="AB35" s="1" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="P36" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q36" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="0" t="s">
+      <c r="R36" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="T36" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="I36" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N36" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="P36" s="0" t="s">
+      <c r="U36" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="Q36" s="0" t="s">
-        <v>350</v>
-      </c>
-      <c r="R36" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="T36" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="U36" s="0" t="s">
-        <v>350</v>
-      </c>
-      <c r="W36" s="0" t="s">
+      <c r="W36" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X36" s="0" t="s">
+      <c r="X36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y36" s="0" t="s">
+      <c r="Y36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z36" s="0" t="n">
+      <c r="Z36" s="1" t="n">
         <v>0.00456</v>
       </c>
-      <c r="AA36" s="0" t="n">
+      <c r="AA36" s="1" t="n">
         <v>0.4555</v>
       </c>
-      <c r="AB36" s="0" t="n">
+      <c r="AB36" s="1" t="n">
         <v>4854</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>353</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="C37" s="0" t="s">
+      <c r="A37" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>355</v>
-      </c>
-      <c r="F37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="I37" s="0" t="s">
+      <c r="D37" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="0" t="n">
+      <c r="J37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="C38" s="0" t="s">
+      <c r="A38" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="F38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="I38" s="0" t="s">
+      <c r="D38" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" s="0" t="n">
+      <c r="J38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1" t="n">
         <v>0.016</v>
       </c>
     </row>
@@ -4270,78 +4246,77 @@
     <hyperlink ref="G13" r:id="rId34" display="Mouser 603-AC0402JR-7W1KL"/>
     <hyperlink ref="H13" r:id="rId35" display="https://octopart.com/opatz8j6/a1?t=dtvH7TGHlC5hQ4n-6C2870dohPsB5H-qnS5LmYI4RAfzJtvhU4okPe9-l4-j2yHqdOanpkBFRQtev6B9Cztm9fWVmG8PSNwCSzOJSR9fCg3k7Uj5H0iJzsuf0ue4j7ciHg_Mkk0YIooA3YGmUrNNZRM8p7WjW8Ts44fd5VY1_Rlk41MlE8uvwXbL6wIKG29kJ1DCQCK_W-2xT5tdHlT9RYZC9AEpTx-nn1VhUkYihwT-wJw_RrJG8jOCb8dHlITkfu9iEwSCxKJy_gEni-xExj-Yghbl"/>
     <hyperlink ref="O13" r:id="rId36" display="https://octopart.com/opatz8j6/a1?t=_-bF77WhASeL4Yk6GV8aKZbacfU_46Bb29Dsla4Cf0V7tQXE6w7039n78cFcbmdmz_gFQYGw-5KhGC3dHtnmKfMEkn1WT4Yhw_QfjpiY9afH2irkcarTEwSrcddpwQz4Ic-hYHtpoOFDHoCSwOysNwnc5rp-67al-RuoP5Qfhgs5g2Z9mZHJgmlEsV50CdIq8DOqJ5oZx06Sq5nxmA3LWxS5zYwBJ6ivkNO7UGY_x8yOCAJtm24LtyzRiOjohb6I3bZMERoTDZP4XpCPWfE2HmbybiI"/>
-    <hyperlink ref="G14" r:id="rId37" display="Mouser 81-BLM21SP181SH1D"/>
-    <hyperlink ref="H14" r:id="rId38" display="https://octopart.com/opatz8j6/a1?t=R-F6qeNetvun7KL4Qr-DAIpuFJsE2n-RWXVWIhyvjPS4kudBsSNxn29-PvHEpq-gBLpzX03i2fKlhnnt-E95cBkDjN2nw4pHSQoEqhhIhUuP0eNLQ4MRiKDm-srVqQ-drb8kai52UYuIP5qnjkUfztIC3DZDIHzOjXhi55c1kwHhRwjM_62gRwZ4WUPdr_IEp66KbwTolG7cu_AC5yTyM-U6gqgm8-wGGFcYKE4KBSfTHDqTFbQNkZsct7CWQfceWO_-iOM0np7_bYbZZ8MZ5tuKWZPq"/>
-    <hyperlink ref="O14" r:id="rId39" display="https://octopart.com/opatz8j6/a1?t=GEL-4EyCMzN5rSY2rHtMak9amUVWNUpd6nsaOdGsLWeUdmdLEQogjKqlp6y9UgkBejei4Nxoo73rRSa6fDTD1AxPpe-nu_QFLC2yDBWfBzaUvZoz5vw-PZPQa_TzSnDBeQGSXWbs_Tkms6Qs3KLzErCK4v-bJVO9un-r2q-S6Dt7Zs-wsc5hfGHtc5zmmL5euaYGC8n4Oc1YEX6Yqwx4j2L1UJZlVNqc03BcfYRbgjx8N5FsGkZg_b5tt4iwFYjEVw6v_Irbh33rf5SmB-b357o0XHnh"/>
-    <hyperlink ref="G15" r:id="rId40" display="Arrow Electronics TLV62569DBVR"/>
-    <hyperlink ref="H15" r:id="rId41" display="https://octopart.com/opatz8j6/a1?t=TgmwRHs6rx6L2MNrGNeXmjNtc9qpOd8V8uqNzLNYzxPXyor6YB4EAMOkdrS8l3hAmokh7wfIJjqPNTrvM7kA2-r6MhDTfHv1hzKkuCBue2BPOZQeEcBF46K-SUmqGG65VvQO4xq9h3whdOLUoKQ3cLNMP2uR-lMeL6Q_97sHYk2bhoQ57d0Wjn1GH5qH3pP8nZqMd29NBExJ_giSknPhJAx6F3lEvL9Yj-4rYa5gJUgrs6OH37cUbCHIPVMKIgKBvwvzHxELGKFxC1BeuLSU-udAZ__e"/>
-    <hyperlink ref="O15" r:id="rId42" display="https://octopart.com/opatz8j6/a1?t=A2gxl1Tq4xbZqkYIXmvupue-rp9hdkmgxuvsVglPVCpm5se22BHGvQhFIier1fmY7cLp4IFI6r4uuDDJslnYSxqKOfGgvKz5-YDpH6ldzhC5_1mX0G5mpf_aRslfr8sS-1aa3mS6d57hed4Oxl_Dk081qIPaJyB621qdZPyEmQ3qQGoHRGmZzFv1baiCHQU3hijnzyO-7liJ7HwNbYGhoI24B_0jiZP1---oOOXp5Pwao0IltaV2GgDsR2FXN9IjkauZi9XMA-kYcfcOamXsCfyKlhQ"/>
-    <hyperlink ref="G16" r:id="rId43" display="Mouser 667-EVP-AA302K"/>
-    <hyperlink ref="H16" r:id="rId44" display="https://octopart.com/opatz8j6/a1?t=IhkoqvMRuVV79daSi7ofY9wJaAw2a1YVXFUeP23TXu9H4FcoQczQto40pVympKD1nNoh7RHP0AUE-CkGaDEH11qL_wraIXVilCJukinS6EqCTRMafUDyjMx7VTvlrWFoXyRLwF3XPaYT0tQWA0pALzMd4Ew4Op9J-CVgd2NU3-zwoP2nswq_ztZrvcMwpaxzla0nqjXKYOfMNWb9yx-fK3cqDgqjH-F7uXMo9MbmPUp8gYA8UAbODNh3kRNBaAriO-bJHl4USoZYyJ0P3qvVBfPO3PoC"/>
-    <hyperlink ref="O16" r:id="rId45" display="https://octopart.com/opatz8j6/a1?t=AMcNk087MBPYO4KFZ1Q6uWUvTdDVJLZjAmZWk06Qg4lZpDvQ7W3W_HLaAK4GFm5k8rY_mHEA0lt7yTxIkrhIXBTKnxdY_NYYj1QjIRAa8Genj9LTt7vzWHeLedrBOcih-LP8TYLDFPssRwG1MyXm-cKtMqcsOOzlvCOrZE1gTzZo-gFHTzfaBhTCywh1YdIJYTRqnDcP4XM_iIf25T4QlGASvU0QeeK4oacmBoVVlLB0FP98KkpIwFPBHKRu7amxqaGmCVbCFe_Fh_auGkT1722y51k"/>
-    <hyperlink ref="G17" r:id="rId46" display="Mouser 581-04026C101KAT2A"/>
-    <hyperlink ref="H17" r:id="rId47" display="https://octopart.com/opatz8j6/a1?t=lIB68rlNRuDRyiIrqjpLy-IKZckE-sbH4FvmqnfLF8iuWC79YGa3cDjORSuUgDF3m7Q5fXxFgEkgr7yCkXvBPzH0p3rrVzY5UpRQDE2lGUpk4YHV6r35Tr9-99yoVHu28UM9fNSL7LqKnJfA--anclLr3JQRt4Ukl-kA5Z6ZglGekzLWJtI6IVr74MntwawwI5fVp_M82J7wHiGF7B1f6JU0iXoy3dbCiKiYRwZDO7Ky8_9ijJ_ieeS6Qh5rNkwcu33jE4ygFtL-pwGu0bc13bUw_Luw4g"/>
-    <hyperlink ref="O17" r:id="rId48" display="https://octopart.com/opatz8j6/a1?t=_Ps-YCwjL8wroUSAreUL3g1-LcALoTG7wwsnh5i_IHH94H-ZNNq1qBgauhmD1n2DKkYu3vHH-1P1jvtFLYG4RgvNDZdJN5AjOJHkNo_1n_mZa5K2s4MCY97epvnUP4ih9c520THAloM_2DTkzGoGMq4V5SQJHV_sBt_mH6M43Gxt9cVjubkaSHNW2lQUhDiZ5uOxH2ysl5kmMAcL-cjMGiijh8PwkELk9P_-AWvv5JeNYi3IH_6GKTXLGL3Va9BnySeTSm34r6aiXn4prYPiG8n04wl0Gg"/>
-    <hyperlink ref="G18" r:id="rId49" display="DigiKey 160-1436-1-ND"/>
-    <hyperlink ref="H18" r:id="rId50" display="https://octopart.com/opatz8j6/a1?t=02rDyWa_bJwMkAA_IrDqjjIiKvwvfS5fgiegS_iFUgwLAi8MkuohbnylUpV50rWeZDIrtn9_UtlYzL_C7wxuYLMS13xPhkadKfUqMAN3lZ0x_nWEPq1diXzf7KnOeamOCEwKoY4PAL4nV8fcquQ6cYcUII3-VLsPsEHBpAAoiesPGIsmpw8kxFCeHwaOsPbraWCvJsCPi5eBgA1LV-EDSs-IK1_NQWbtZp0zQ9PBU_2xmx-nrEONl-wApUuzJ_fM3u9PI5KtCD84pRDH-c8Ttp9h"/>
-    <hyperlink ref="O18" r:id="rId51" display="https://octopart.com/opatz8j6/a1?t=4Z8yQeECmR4C_z5gZdYgUOSOHyk6lk_OfTENDZKAFXPT2tQGZiBsfNSIX7Obg_bNUM-M-P50rK5grVCpKdHOUirXoulna9sx1Zng_TssD5fGRSWHYW2nKx897nAhAn6sw-FFfzc26gxquiGhOEwj5hgp9aZFiN3P6l4AgSlLpOX8SbysAIrzoJzD7q-RTbDa4PCz5SGMuPeCVEz_6OYZTPZzg8BQ9qfO_AhS-1F28C7SdgRZHm19DLRwOSi1jSLYrTB3SvrmW-6THINXU8maj_s4"/>
-    <hyperlink ref="G19" r:id="rId52" display="DigiKey 160-1646-1-ND"/>
-    <hyperlink ref="H19" r:id="rId53" display="https://octopart.com/opatz8j6/a1?t=fzi2Mzy-EcZOdKC8ToF-PnqDMIsThTuC_iNzvBIBhBwifxpB6xcIPJ99q6uUpk0WtwTozeQ_XXufEFVJpKTEYVWriA_DkUl4mjfmRjN61EQJ-axdrFHdNvBJk6Zlr1m7ypSz02jB49M4ItVkVmVCxpbpSCIEcsXTVivjGhgIjWNGGjrkZxY67HFO_1hE1jXGOXUcxRSOStRTrhsLjRE0UmfcqCWO-Y_nZglSiQQpXdsGUEPfLn0g0MMO-0P4yTS9EFiqJL7NOHfPFpxy3ZPblW0"/>
-    <hyperlink ref="O19" r:id="rId54" display="https://octopart.com/opatz8j6/a1?t=-RJoa4vc2RNfxVMeTcMfx0QkVbhyUP4VBt6N5E_Pfv9v8iH9fNAG3yWuq3XXXTcYpR7yIeCajqoVfDldw8qNSPX4cMRlu8HHcPlo5uFFV4sbOeoOKudSD3I-eXuedEF8v9Hg5ieDrANhIulAghOZwwMfycBsW5xUCjOPCwRBQ9-S1YV3RN2PcXEZ63vpzSaajD-DOYuz9h6WcOIWyhBRYKABJoWuszE3iLAxdeEd7uKQNw_-eMUZX2Yh8YtJ3sIQNILtILe0bXboIZuShauCyVh8FA"/>
-    <hyperlink ref="G20" r:id="rId55" display="DigiKey 160-1433-1-ND"/>
-    <hyperlink ref="H20" r:id="rId56" display="https://octopart.com/opatz8j6/a1?t=JGMy1S1qxhcoLmPEALYDjxyIdX_DbFoXkTvyOq9BaNCLl_sSGPFbrw2toMYAd5_LtMgJjSkf2WRqwdc-QmJL1Kz2LttTJSCszc3dSnTSP_QbmTSr2GEZJkewN8nOmmFFhsgQ57t0i5Fsp0jMGUsNv2Fyegb_uNT2QjsZp3OlTTqXnO14KoZCk2dqIW1hlCSvuD4TKoucYi4Ap2IzUNiFVqhtoVdHYTZr9lB5EipVCwEtJegnegx5A71sv1QkslwEJ6x75PYVGJ2Hg_bx_Qjsf1mX"/>
-    <hyperlink ref="O20" r:id="rId57" display="https://octopart.com/opatz8j6/a1?t=Pu5jrhmsrlcz1codkQWlwt4Ssq1b5ZrTqGMRyLwKgJYehpc-3V6dWg_vcHzjmOzcT6SK6qHu4LgKq0PsKTduK3doJ1In2XhDwYDdv6-kA1isCGopIG5kFpg998tLnwLHByFCC4P8x-FtipurXGxqzWFS_Lo_qwUhcPs2dHNVlYbl-Dn_dIfOHhlPeSIFCb9ma1LlCF71ft8zp98-NpC7c4O_iVfu24VQpjNrcCaamGOqk1FQJQ67CW9bZ-kEX4rLrRWoWiCl2OljFd8qMPdEIY9S"/>
-    <hyperlink ref="G21" r:id="rId58" display="DigiKey 160-1446-1-ND"/>
-    <hyperlink ref="H21" r:id="rId59" display="https://octopart.com/opatz8j6/a1?t=kaaMQ92alPC-mX1q_ZGaIAsByIP8IAfVOF5lfs1Gwz0GyYmFJT20LQAMnKWKqcGUapWpmUevE11u9QG_Zt4N2cbufJyxAvB_hsDDpU5GdGLFFg8aRELG6vSIw4g1DHyb8qui_X3JE7Kv6d53VYXTIy_-2KTTqX7lbZbfDj4tqDGt_OE8rh1i0AbCo1DB02YTOogqYvRjTzL2VLFEqIJRbWJeQVZqZoEVV0RLu4G_iBGxAbu_RG_sy1ftqtni0Kd1JnnE9Y7v-8f9h8jp0rGYD4Nv"/>
-    <hyperlink ref="O21" r:id="rId60" display="https://octopart.com/opatz8j6/a1?t=cyyzQSuNi4YznIxyw6TRFNKGbTXRzxC5ZcNPpuJin5xNBIlLu_K1X2mSfWW5oyud5GAn_As6fHTD8wbHCJVrDQF-E36eR2Id_0R_2GK_5RanCld-6-RYafY0R6NfILeaRRF_Utbd4vuZL75yVAXhDKEfHRA9GiLzRpMgVGq3gVOzlQzVGPTvpmtfF2YEEmTW8UUV-LoDEVplD3HgElEFgKCEC7t1XzKqI9-FjCyTC97Vt9K4G9hvG9zAnjnLuUvlz7929kVwiJJnGjjc9czGRiPR5A"/>
-    <hyperlink ref="G22" r:id="rId61" display="Mouser 833-BZT52C3V6S-TP"/>
-    <hyperlink ref="H22" r:id="rId62" display="https://octopart.com/opatz8j6/a1?t=YakmmgQZ2cuLiGXF1toII5G-G0v2IC_yywHbJZXniYUXIqRI1pg1zDMcbJzyC-VlZDZq-PiD0vZtOyvd0GoCvodi20gSinDFcOredtVYyqfsOWUFuYkcVN4zsKS1pb52V9Yi_7dAQDXMCVfh8uclms78nVtGhlvVPQwzg8BAeZe401KkCHuP_SFDsfiYs_sUmkdENTloxHu1eWAtEuzBRmWoBq9jZvVpkWL2xyZpQRVvIwtOPF0Nv0kZRIN7SgNCqS67y40Ju9i1nFcEdWCemVpgHoU5"/>
-    <hyperlink ref="O22" r:id="rId63" display="https://octopart.com/opatz8j6/a1?t=rJU4KNO3Q3bWDrLtrdbN968lcP8E3RZTfC_NGme9BH7yuYQHhYqU4D4zDFsqxncamqoc1JZYRLx4s5sJVvDh1c1VKcQBLXLopH3Ntis1evMMNY4dAz8LsCUjT19VmuwoudXo7loyMJ40aKYjgvLueuRmiB3hqxSv4RHIOuBywIu-csZDKFlAZ1_-CZu4_MaClUtCqkWprZQIQeL7JhVYmzcADqqi-QcXjsBewka6lNCNkWv4FS9IZ7mM9oRIWRONU7UKajIlO2pRYGYDLoG1U_6L_L4"/>
-    <hyperlink ref="G23" r:id="rId64" display="Mouser 520-2333-250-BNT"/>
-    <hyperlink ref="H23" r:id="rId65" display="https://octopart.com/opatz8j6/a1?t=E4sWF5WTw_lHLWSvAVLaNAzKgMSFqkzfmQrkXIOW4kTxYnGKh2ZcF4ED_wLkfNcr93Kjaubh3KIh3s9EdYT06RTbiQizg8ofICyxXgW7HQVLL018MxC8gDd4Myz6-tGLEpoRIxErrqSp4oiyqcbaQ8dqXf3EokFkoDSr4WYYXQQy5cv7HIvouadDMuti871udI9ctuTZ0GyrJLdcb8xutvncf-fNAclQyur68eMM1zciKugdpPguxHoDCiaSw1pFNDZpOGJeQLWBOM-kCrYhtjk6C2Ld"/>
-    <hyperlink ref="O23" r:id="rId66" display="https://octopart.com/opatz8j6/a1?t=mSq67AvCLCLIiFe4k_bRHIapePBV2HDhPAm4LaNtFOF72rhQRyzqlti8__PtH9KK8gHew9QsPNRf_7ALYfodUfqVELOdP63fNnYypHeWGkEhvfwydE3pfK5TQyr5u-OprFnWh-wdFugvv060ndsIpXdoj-5rYiTw9jToj8XHACz5mGTcMv6zJg9Ru_JlSgEMZRTVQ5tdDQ2t-s5OnZF25NtDCUaDZsApjuwBbDkcuEGv2Pq6oiSFWHyqidSn07QrTkchI34YdqEJuxyo03moSlrT3XY"/>
-    <hyperlink ref="G24" r:id="rId67" display="Mouser 798-DF40C100DP0.4V51"/>
-    <hyperlink ref="H24" r:id="rId68" display="https://octopart.com/opatz8j6/a1?t=GSvJ3-ybhEUhXL10fULYrnPWV_7Rl3bYrTfgtmWkJ4xAvP9aa8qSRz6hJSncoZ9ilhxJA3ZeZOQlNbhnW0bZlEiG0ODLU_EHi5nRWcjB6x6AvqmkQt9j3_myTpSDb1-EcwyRACO6fIFarDlZ0hCz1k2_xVBAvFUmxeZCWMbiBtp2h2Gjd4uez4oxkNI5wUvHFUhPbJdA9gVJZhxAaA9ZEvc42QAoHDwrIkv1zm7qmc0VOc3b0K0jjBz2Pb4YGB-KT0ucUbNIipbvrrmt0ehtz7rPX7-p"/>
-    <hyperlink ref="O24" r:id="rId69" display="https://octopart.com/opatz8j6/a1?t=Ry70Y5V9Nd6czZK8G8TPxUgDHTBWSkR_T88WM3i1uDvJfLVmc5lS_9kK1TwfknuRdZDtpmxSBE_-VkwO9odNjJ8LsF6epH8ti4p1280ARI29IyfnJJoiWxeO7wrMfOIhJIcrDG6MZt5YVKd1YFjP6w2sEYUA02WpvX5_txM0cVrqNEqS4w6SUr-X-9v8fjT3TqB6PZGFt5H6KX6x6navWOhMYduSpMRKl2QDTyyO81ai4hQ5OxpnTHQnncamfZKXEx_utSsFolALnnfZ_O_MTJGkJic"/>
-    <hyperlink ref="G25" r:id="rId70" display="Newark 97AK4032"/>
-    <hyperlink ref="H25" r:id="rId71" display="https://octopart.com/opatz8j6/a1?t=zyTuPDsPiVdvT_SCqBQZ0B6NHSnl5OCWlpV24EwKKr4OHIzXTAk2rZRu-As877AQhllMacDwJzuUcY3GRedI7RhstkwCXEhmPQpbtEYUOop0qOMarB4fqIPrKPM9KCwAM2r66mjRbg1LpYoGD7hUmyVP2cCyCFaEVwSd85m-dADJen57fGROknXicn-PvyHewqqzVH8lv5Lr4a-c8QVePY-jTfOnQSq6DqJ21_f-Jcrcdba3fUH7Q8RL1sW2NaszEO6yMX9-T8G6GOmc5FtPQIoAzC4w"/>
-    <hyperlink ref="O25" r:id="rId72" display="https://octopart.com/opatz8j6/a1?t=97pBINGDxY-yariYHpmZbV0OICU1Pxd2KFbY5E5wC2NglJWadSQfg3Lya5BaodT-erXPVSKbdi6dVwiB8-HXa2raUUqdxMdgdRRVYneq3k4a7Z7anfcCVlNzVPKns1awdtd5owXXbX1S39jwZ-va2pWfU_E_1VBP3uXVoQoIJZFaMi2GTZIp6x8UEiYPdF-qoujbP_V20_AXNmYbZ1xsnQalyXG-havOrGkRwrQz3xqW1yDG4FG0k7ld0D63epRPZGyxbdoo2rfaaNXHPrjozPvdsw"/>
-    <hyperlink ref="G26" r:id="rId73" display="Arrow Electronics RT0402BRD0712K1L"/>
-    <hyperlink ref="H26" r:id="rId74" display="https://octopart.com/opatz8j6/a1?t=1A279XklIitwWJEvO4vF-b2TjjaQAIS6AU0t0aypY37HTGFEQzvMQ3NtSpkhVjfhO-jtiRYPY1mdDoEVi7T8pV_EdJVvRgMEVny1PhSkKG_rsXbBmyIeuaZtppH4764mC-oCGclnq55GOY4CYzhpW_iz313CaAbPcNLAe_ZpX_A0837gpOVmHu6XS7IRo19sggohrMoXRHN4zujGpacrKzwX944OBcil1gKG8FjgkW6W-DQuoKS4ogjNym0bQxTzU6LXCQ7PkvIzUCOKQqvjThu8uws"/>
-    <hyperlink ref="G27" r:id="rId75" display="Mouser 842-LFE5U12F6BG381C"/>
-    <hyperlink ref="H27" r:id="rId76" display="https://octopart.com/opatz8j6/a1?t=NHw_We2NIaQQdPF_BLRd_EhqFIxHdHUAyYfMPjIi2dFNNOl3_ZMWvMwBoVNw6cCMDtEIlwhQu5BKrR_pH0dqhBO8j_ZZiwwzby6Q9plcp6U3yssNoqk9c4FNrUGMd7nlraHFrX1MRke4RC-juci68_hKUdCKi5rBdULtVnJJEtDAUHXuuFRw2CtpRAeVCZ5tPuEoIBtHRHa2PMWeGknLC5WN7tdCA-dFDQCTY8uSo7Gtr5KN-g1oJ-Nu_zb8s88R3UFgxP3IF9QiAM-5NALq0e-7fVp2"/>
-    <hyperlink ref="O27" r:id="rId77" display="https://octopart.com/opatz8j6/a1?t=vi9R2ddUfYB0Z-DMAq1x_YBmTkYs8GNQAc5dgp1sGmgQbFw4MS-weogcc_MFmzV576dKqpglTSQJpUP5O_Wwd2ISQyV8fsupxcIDB8s0jbR6TXHmaKkgmqYre37OgByGT7c3fNeuRU1lYYaso3DtLeWQ_jz9IQzN34RWCeBiXbb793yMUV3F6ijxqVpCPCuH9ZEs29KeCO7lsQc_cpj7--Dtl8HWW1PQ3E6BCRVgEMCL-VJawjvvaadjugDdyZQyRQcwSHMdAjRSEvq2-U8kJ6wsWYI0"/>
-    <hyperlink ref="G28" r:id="rId78" display="Mouser 870-42S16160J6BLI"/>
-    <hyperlink ref="H28" r:id="rId79" display="https://octopart.com/opatz8j6/a1?t=TDow5Ec7EHeW3_9HjQt7dBbG1yhsK9_I67TrKz99ijrswy3WIYZcYVvBHiZOP2WbcoG_HEBKfPV_GmiqWeyoEE2BLYBOVTYa-F6XZfhY4gfJpfiSej74wQR76GZ3iJSlZelb7DALve8kAnkXedvbIfDTx65RXiU7QOQPZxcIH5rMfaQsGRnQg8WQPmjQ9Bl6UTf0LmMSwipVlqkklfq15UPLHvBuDiW4qPseVRaUyrN9-uSZj2sNr0fmEM4PJNUvU0nb142qqYbZYqup9Iw-kgcGbdui"/>
-    <hyperlink ref="O28" r:id="rId80" display="https://octopart.com/opatz8j6/a1?t=OiK2wmnOg7L0CXEN2X-hI5yq4KnG7p3CN0iC3psSIlx5Bu1-y6d8j4oaIbY393oWPxAxvKKaxCTiJyPwgdUoZ61T8tBQpI1b05PFkkNI4Y06YAjBXuHrOt9EFIAaQ-F8TvlfR9QrQVrYi0R4Yu15e4bEJvfXkUVG12Oq3Ah0BbyHSn-NGaOizoPg6SqcBVDJhlZWFDvbcbS3Ol9LHfQFCLPPvnQyAOM7DZDyrS3BbuCI6Tch__vUiuTTc3kKTl73_qu_aj4Nqf1QjEfq4LXnrtFCHPT1YQ"/>
-    <hyperlink ref="G29" r:id="rId81" display="Arrow Electronics IS25LP128F-JBLE"/>
-    <hyperlink ref="H29" r:id="rId82" display="https://octopart.com/opatz8j6/a1?t=3t6UbzS-NE1YVYInzkVwhuqwODyKnlVUnrXj_Dm6E3fGBif_s3yinz1_EDg_kroJQwO4cJvo1P1ZN8_Rzf_MGBpOIhtSpGv_vnUGa0SV1mhkoMkxdCm8ZTeI96kgalMqP6k90a_NVaPbpXB9moM5MnymPXVP-iSljijkTjzl7PGMFPtgVHCDTHciFmvRkUlaa4knpAGe5Q7wKZOBB7Xlylo9Ns-owcbkaJpk1ejUjgr0Th2kkDIsjwb_V_NfesCWltWS_zj9pw9JbXQ-m539hvHG78xG"/>
-    <hyperlink ref="O29" r:id="rId83" display="https://octopart.com/opatz8j6/a1?t=GHBxJ10kL47vjux6hTkOFHHUq0NqtCHDu7rOd5w34bWCYCKZoxOLcoDL9J3T_oKPQLCMWzqcLyIxt9zpz49i9bq4snbmZVtSHhM5Gom0kELIeg52ZOEv2bxlJHQ46CfZ4LFp5EataNJJAsb13uCmMRjvIYIlluJLI5VZhc8tQjLds2ivTA5kjVvc17cROC0J1gkQT4Xx5YcwSAqFg0b7uOtJolOiysLvvLyRIm-t-bTwqDZU3jLVEtNvbOSxiVWVWzZWbYHfMZa0C-fT5kTv2A4pQiGy"/>
-    <hyperlink ref="G30" r:id="rId84" display="Mouser 579-LAN8720AICPTRABC"/>
-    <hyperlink ref="H30" r:id="rId85" display="https://octopart.com/opatz8j6/a1?t=GEmbYKTbx4xn-BVBNFTRkEU_vMzSHrxyG_flue6nv0_DepKR45Z4hViW_-oqD_4UfL80Th61R2CMdCOfiwcztVc2TbHVdVFHSzoFBwCsyvO-MueXTq4w_WszmMdEWY-gwBPybLwMWGI21SRp26BMEVZZQb9d-fcrt3ydPGShXuZ0h3Yjo6nHKcGdcMWEIhUM84qmlMPUUFXx8Ie1JD7R5F75oc26YZSc-zoQo-4krW7e5u0YEcomtk-YMa7jdZC579zZHoYGZEVUzYu2HhcvqJ90olQ"/>
-    <hyperlink ref="O30" r:id="rId86" display="https://octopart.com/opatz8j6/a1?t=acaDbe9ReO2_lo3YTaa0JocVK9CjjgmA4ewAvDD210E2B3tfheiPFZcb6dYnFD75TdNBe33tHID6qz62H5iUFi_LrfTOs5l9TizaZLRIRjVJNr8fh6JzwEYYdxuOap-Silr-dpvMaYY1salofpP6mYXO3TFpO4-ViDEzYtUxsxHUdDLJTywQXkfa5mHxhe0mm2HD7HgWpK39o0pvn6kj-Rw1xYT1EblybDrFA-HKLJTyAw5Kx5C8V6OAOyn0znMveeIQResgIY-lyAjD_76oEn6IUnehTw"/>
-    <hyperlink ref="G31" r:id="rId87" display="Mouser 229-CVS-02TB"/>
-    <hyperlink ref="H31" r:id="rId88" display="https://octopart.com/opatz8j6/a1?t=e7COkKmvLUBCVBAhSWIP1P795VAuu92Mwe0bzyzUtm63aJ2dZMQYq9o0c6lQSnyLRx51gEDc1hgu-B4sZ8yu4imvVGAummUkfJCtHhV-G8VJ6HOU36DadUwmsitz1H8OxoIB_-10OyO2yDU9JbA9uNMoXxYyg1RuprQgd8hmLKdNyOmz-Z3tdgu5_mPtE2UzFfZc0ivOitCr15dvggkMkK6reJN0vjDHLK5S1j_q773Qe1ZRBhBMYSMxcxI1Gx23cesoTdqg04gPTTllXYKeH2cN1TxJzg"/>
-    <hyperlink ref="O31" r:id="rId89" display="https://octopart.com/opatz8j6/a1?t=MuoUORcf9wegHACEDiAx7DbMsTpjjE4DCgH7Pb_LmNdq-R7I1-NC0KJN0uzJsNFbyHP1n00BwkUeGqPQFKQjPkKqX_-G5Vun_9w6_x0jYYdQJWvZXtWzgVMgW5v7zuTMdhjrhZgJqMzYRdF50l_tNfGHa-M9gDY6J5WO4Y5RAG1IwdcSodFEgmnLnqnPlX-9PtMVr8Srk0pdYXNon6OMXm5TOe2XX-WFnw1mkkftLTyvLPtRpuPE8XfA4pjwh_gsxdUjbhzV85TLPw5cO1iZM2CZfxzZlw"/>
-    <hyperlink ref="G32" r:id="rId90" display="Arrow Electronics 10118192-0001LF"/>
-    <hyperlink ref="H32" r:id="rId91" display="https://octopart.com/opatz8j6/a1?t=xGwT-_wxm-xxaVjbOcuqPEqHxZnWOBl39WypdCzKioq7NwL2xFNZZi5uwBgfz4AE5IhXFPIZS4OETurpHl-HcYcDJsG6MEVWVoIPyKAQoMgUmnUg846rwDKUL3GVaWkgyKLbpGkQVWrV79JxHCWS0fYt21S3Oy--yvVM7KypJPfat2Xo7y4SqSRewX8rQtqrdOAyhWzUsoqJr-qw7IfCTsOHaieSzKzG5iuFqXIhn4izTcW25-Tl4rttqumF6zQrHT0oVX4OwOzOPs6-zlPwUWeMAhPJjQ"/>
-    <hyperlink ref="O32" r:id="rId92" display="https://octopart.com/opatz8j6/a1?t=UoF7ECcaEe_D_84vCdLpDp39F3UvENsUx_0xifbykmhoCd48kuAT5JTvKjdMzJzvIe_nwkmaxKsCJgnvo8sYMCxKPqNeHCrh7sfMbOCjXoTia2IZZzncSLPZ4yc0oClJhyIa8_L435oRc6GtCeQhY3cCRXAHEAtOI2MutEWKrLqAwYSCXcTNHzdlIOo8Cu7ws_DvloGIemNJaznqANEYapr6FJ92TM45Rh3sJfD33rpiDteTFDIvpoQgX-aUhHQnV-PMGj8AuziFAb7g6D92bIZYAfqptw"/>
-    <hyperlink ref="G33" r:id="rId93" display="Arrow Electronics AC0402JR-073K3L"/>
-    <hyperlink ref="H33" r:id="rId94" display="https://octopart.com/opatz8j6/a1?t=j748atneLsEWEhDK__DYCImV0I1d1jv-KvoVj-JMLP1UlAgFAP5RN4zjx0tgpmtAa_e_PmJKEIA7jJhNXVn7-yy2PaA20LJgMmx5mQXlllccNwWwkgGRObA3du1nhOqD38mtnRVELKaIeEmMwpGHvRUVrNdKSg1VtL2GwSK8UdzNiW2eManuz7IUCGXyMRjKxcTCSGZlUjOmbaoegKpThVUhhuqQttGrnI8YsR-SwScBC4bNjImvWoNG8ncXw-Bc6_Gu__xz5gpAKy55dEM1TRVOEENT"/>
-    <hyperlink ref="O33" r:id="rId95" display="https://octopart.com/opatz8j6/a1?t=kM2oQZCTN63woZ2J-R_QGI_mWWfcA3hYWb9XDJ8I5wjHKx9hWIhqzoKooSpm7Bhgmq3-gt2BFyFlkUa4_oMF6C6fOUAeZpMLvasPs8Xlufkss7xF8gpG46Sw0Q0L4QWxgiix8B8kFRnYgtQ5OT1eqQG7A8Ur7iWvme6VyvdCv-ohQ2pw1JazxCR7ikNz5BZmUEzxir0q5dSkiux6PbvTlkUkLE5-f8G8Hvog-R9ZkiBJcDOk7x5T6Khy43lVxg-6y5FB3oiD8Am_ZUkCpYY6LiBR2ks"/>
-    <hyperlink ref="G34" r:id="rId96" display="Mouser 603-AC0402JR-0718KL"/>
-    <hyperlink ref="H34" r:id="rId97" display="https://octopart.com/opatz8j6/a1?t=EbzFpn45QbztmSEVZdek2jFDL0yrs0RVmck3uHBzOFY5YRYiO56VZWBrkYjM9BIxRZ-hpK_lHlS_6Vn4iaI-lmCRbDaYeFW-fLBx5GAdnU9zE1hCyv8Wt4LJLX1CfSZSPUb6Y_9YUpR_p-HjKzewLMyQrRxO1qLk8oA3dxHSq6xnPQD3QvQdDZ9dyVqDUDetCLHwboEMLZ-NglFWMA_DGGSrd9qFMPLwC6duMjlppRBrtRmSX-E1PWS3KacoYl9UQvh3Kj-66jLlTbfRhpKOppeOeyOj"/>
-    <hyperlink ref="O34" r:id="rId98" display="https://octopart.com/opatz8j6/a1?t=lHsPPhSDmyVQoXi-roIdbx_1I56VikOBKPyjcG6ZI-9yotLkLT-j4LEoIXYhDshoGZqrd75vw6HTXzRynSKU0aSBszSB22KfYwDiCJF5NJ-6E-rcYvWtEtUE4iVa8-Q0BwfQV0s-ktzWnhe_kjk4sqACoecU-jKmixqP1SBJyc2CplydhuldmLZYJEhIzDt76D1V0gSBoKlCpt9ZhwlL_RTx5j5X2TxDTSjlXuGgKWlHjEAHTOAARhfMjLZ9SKM9hWQNgr49bYni6UZJjRSAWW-Dzpk"/>
-    <hyperlink ref="G35" r:id="rId99" display="Newark 59AK3056"/>
-    <hyperlink ref="H35" r:id="rId100" display="https://octopart.com/opatz8j6/a1?t=I-hWLsLPiOj1_DhHYBdF88CiYoErg-DEEuiPkOPYYqhYhG4MQjIY3RwQTjme3M5YoZXbtIjqEtZ61SZZJve1TRUfidCDeSRBsFxzLnfONo_uWhEzfs5CrholaJMbMsVY7zVxGS0pDUKexLQTg8SQuqKVobqHKnmO9Om7gqfHxqUC74yaaAr2OstH7Y5eKvhKtzzhs97-yZ3aEE4J7Hca1-ZCujWKfPDp-aHX_sHRTbrP5h07knU3b_4DxbmbLsNF0w6d-j-dNYdWP8VgM3TmG0zVNq5E"/>
-    <hyperlink ref="O35" r:id="rId101" display="https://octopart.com/opatz8j6/a1?t=rPjJZ6CqLGe9iLMXm09Bm4eU2FEsBa5dly-XC1deN6qKsMyPeiDrr9HNubztWp66pl-9mKGy1VRNuTFNQS7UE2Hkff3ZUmTKGhQo8GpL_kM9PkodW7DB9siYqTC4kaJ8LeUL2SYXWvZqkIVeXiNRJzTgikMUeWPDMI7E-zZEUN-iHOI_2xXHYSHYs3MIrs8aTkOoAH2qzT1NFeKAwqv5rJtGjjHrSUsM7zDySj1MehAmWlC0u2zBIOSCwIFd-qSxR9JjHYlebCbgCVK-xWWcXwHDfBFR"/>
-    <hyperlink ref="G36" r:id="rId102" display="Newark 49AK6954"/>
-    <hyperlink ref="H36" r:id="rId103" display="https://octopart.com/opatz8j6/a1?t=MQuAwuMoCM9oQEU2Wwrv6S0jntIdg2z5ipw7ciYWmHy8eWhSKdospqoUzswygQmf7DcgVpIzjibeJg0-gP0nrgR8RMxGMaqCEzqi-qlYUYfB3vETjakmA_RdW_7r0aCS55rBE1IpTla6h2BEj-hbEZszuIm6zlObTCkOBAODeGIUYdDdNDB-yPKM43ELiRps9AgraF6UGzAyEn3SP6m4cd5d_wCtanmq0KBA0eD6BhLFrcr2EESQ0dEWg4a4vrFujNfcvhHapSbc37zi7pf9BOs-zaZn"/>
-    <hyperlink ref="O36" r:id="rId104" display="https://octopart.com/opatz8j6/a1?t=9NjSGnyaE2OiXrOCtPJMuyk0xKFm82ZrRjkULZpQmdRv775FwxilwGCUZpnlQWU1PN5g4dwlwfiJPmbgc58mhlI092ChV7NUzrfSF2779zM7t2xHqJ2Fsbj6-WvOTynVKOgWGk-T2mhOOOuCP5z6hyBvhp6alDDCxlQHQkkNBKdny2CPzlbYHzPtyQJHazfYb4rxnZYFPuGFm9z3xC7EjnS60jiKz2PIUxJHi_2CjRrkZ4EPgrqJ-2Cj81AASuZqEVq5lFyaFAnoU9ywNNZ1POegS3Ed"/>
-    <hyperlink ref="G37" r:id="rId105" display="Mouser 81-BLM18PG121SN1D"/>
-    <hyperlink ref="H37" r:id="rId106" display="https://octopart.com/opatz8j6/a1?t=1qH2d21Tvjz5pRpJhyud69BzvSOdXGWB9wG-cGwonWlZxYL_ZKeUv7C9IW7pXDEV6iwk2onNSsQfMbQ-SIRKhqt0tqeUUPYtbxfCHORahdoJvSsvOXB8dZBVdmABDgDeD4IiWH2_TmQWJFUrN_SsaMlT2im6bowHyIhyXbbNNXgIjt-V5V7dLyArDejZjbR3Ki3uk4m5Peyd43hDxfqWj2Fz38XvrdM7z78dK0pxtgOmSjSTAcBOD_XW1tudS1l9OmHfhXT3pEgWC3hd-czXF3-Gpw"/>
-    <hyperlink ref="G38" r:id="rId107" display="Arrow Electronics GRM155R71H471KA01J"/>
-    <hyperlink ref="H38" r:id="rId108" display="https://octopart.com/opatz8j6/a1?t=f0Ukf-STZBo7bhooAROoCLCltSPN55tWcKI4ZS6ZZ5om3Cy96Hvd3irAEMHgo269mQQydb5_pV59DEb4m8cCPgV_xK1ieexkguHI6Zs1eYiJGs-pHSw09-quPcqb3gxyO2ZL450lKOdei2voUNTsDdsBxYK1r_H1qBR-ZCcF8ldFcook2ypYIBDJY290lZTG8s2DEY-K0QI7TWsKVSr3UUhOpG_E7-Fx9PiTXwxWN1Am8-LmoLu0fjjY0H29buWd2-eCPA08oKOfE40MeerMWi9onZs"/>
+    <hyperlink ref="G14" r:id="rId37" display="81-DFE322520F2R2M=P2"/>
+    <hyperlink ref="H14" r:id="rId38" display="https://octopart.com/opatz8j6/a1?t=9Cr7-k-NMVDZL2fACYvcAPvm9HA_Q8ESxvMDcPYvTe7GJyBvhUiDs6C-skCNCkMi63DmLZhhkxkE-dEqm_fdj3jtlD-jNPF9BxH1OJ-zdGqd3fabyJi4hBIAOSMg524GzfPY4G1o8Ya2GTJHk7zklVDaQ7U-jKySVu4BWjHmE-8jSHl4nKoXDv6ordOtAZDH-m4J4GduFr9hVR436w-o4R9_k3jLTaOT66tB1z63o_Ozv2k55R38Ssof8Bzo-XyMgF0TMGioVITBKcnOvEbW2JFicCebEQ"/>
+    <hyperlink ref="G15" r:id="rId39" display="Arrow Electronics TLV62569DBVR"/>
+    <hyperlink ref="H15" r:id="rId40" display="https://octopart.com/opatz8j6/a1?t=TgmwRHs6rx6L2MNrGNeXmjNtc9qpOd8V8uqNzLNYzxPXyor6YB4EAMOkdrS8l3hAmokh7wfIJjqPNTrvM7kA2-r6MhDTfHv1hzKkuCBue2BPOZQeEcBF46K-SUmqGG65VvQO4xq9h3whdOLUoKQ3cLNMP2uR-lMeL6Q_97sHYk2bhoQ57d0Wjn1GH5qH3pP8nZqMd29NBExJ_giSknPhJAx6F3lEvL9Yj-4rYa5gJUgrs6OH37cUbCHIPVMKIgKBvwvzHxELGKFxC1BeuLSU-udAZ__e"/>
+    <hyperlink ref="O15" r:id="rId41" display="https://octopart.com/opatz8j6/a1?t=A2gxl1Tq4xbZqkYIXmvupue-rp9hdkmgxuvsVglPVCpm5se22BHGvQhFIier1fmY7cLp4IFI6r4uuDDJslnYSxqKOfGgvKz5-YDpH6ldzhC5_1mX0G5mpf_aRslfr8sS-1aa3mS6d57hed4Oxl_Dk081qIPaJyB621qdZPyEmQ3qQGoHRGmZzFv1baiCHQU3hijnzyO-7liJ7HwNbYGhoI24B_0jiZP1---oOOXp5Pwao0IltaV2GgDsR2FXN9IjkauZi9XMA-kYcfcOamXsCfyKlhQ"/>
+    <hyperlink ref="G16" r:id="rId42" display="Mouser 667-EVP-AA302K"/>
+    <hyperlink ref="H16" r:id="rId43" display="https://octopart.com/opatz8j6/a1?t=IhkoqvMRuVV79daSi7ofY9wJaAw2a1YVXFUeP23TXu9H4FcoQczQto40pVympKD1nNoh7RHP0AUE-CkGaDEH11qL_wraIXVilCJukinS6EqCTRMafUDyjMx7VTvlrWFoXyRLwF3XPaYT0tQWA0pALzMd4Ew4Op9J-CVgd2NU3-zwoP2nswq_ztZrvcMwpaxzla0nqjXKYOfMNWb9yx-fK3cqDgqjH-F7uXMo9MbmPUp8gYA8UAbODNh3kRNBaAriO-bJHl4USoZYyJ0P3qvVBfPO3PoC"/>
+    <hyperlink ref="O16" r:id="rId44" display="https://octopart.com/opatz8j6/a1?t=AMcNk087MBPYO4KFZ1Q6uWUvTdDVJLZjAmZWk06Qg4lZpDvQ7W3W_HLaAK4GFm5k8rY_mHEA0lt7yTxIkrhIXBTKnxdY_NYYj1QjIRAa8Genj9LTt7vzWHeLedrBOcih-LP8TYLDFPssRwG1MyXm-cKtMqcsOOzlvCOrZE1gTzZo-gFHTzfaBhTCywh1YdIJYTRqnDcP4XM_iIf25T4QlGASvU0QeeK4oacmBoVVlLB0FP98KkpIwFPBHKRu7amxqaGmCVbCFe_Fh_auGkT1722y51k"/>
+    <hyperlink ref="G17" r:id="rId45" display="Mouser 581-04026C101KAT2A"/>
+    <hyperlink ref="H17" r:id="rId46" display="https://octopart.com/opatz8j6/a1?t=lIB68rlNRuDRyiIrqjpLy-IKZckE-sbH4FvmqnfLF8iuWC79YGa3cDjORSuUgDF3m7Q5fXxFgEkgr7yCkXvBPzH0p3rrVzY5UpRQDE2lGUpk4YHV6r35Tr9-99yoVHu28UM9fNSL7LqKnJfA--anclLr3JQRt4Ukl-kA5Z6ZglGekzLWJtI6IVr74MntwawwI5fVp_M82J7wHiGF7B1f6JU0iXoy3dbCiKiYRwZDO7Ky8_9ijJ_ieeS6Qh5rNkwcu33jE4ygFtL-pwGu0bc13bUw_Luw4g"/>
+    <hyperlink ref="O17" r:id="rId47" display="https://octopart.com/opatz8j6/a1?t=_Ps-YCwjL8wroUSAreUL3g1-LcALoTG7wwsnh5i_IHH94H-ZNNq1qBgauhmD1n2DKkYu3vHH-1P1jvtFLYG4RgvNDZdJN5AjOJHkNo_1n_mZa5K2s4MCY97epvnUP4ih9c520THAloM_2DTkzGoGMq4V5SQJHV_sBt_mH6M43Gxt9cVjubkaSHNW2lQUhDiZ5uOxH2ysl5kmMAcL-cjMGiijh8PwkELk9P_-AWvv5JeNYi3IH_6GKTXLGL3Va9BnySeTSm34r6aiXn4prYPiG8n04wl0Gg"/>
+    <hyperlink ref="G18" r:id="rId48" display="DigiKey 160-1436-1-ND"/>
+    <hyperlink ref="H18" r:id="rId49" display="https://octopart.com/opatz8j6/a1?t=02rDyWa_bJwMkAA_IrDqjjIiKvwvfS5fgiegS_iFUgwLAi8MkuohbnylUpV50rWeZDIrtn9_UtlYzL_C7wxuYLMS13xPhkadKfUqMAN3lZ0x_nWEPq1diXzf7KnOeamOCEwKoY4PAL4nV8fcquQ6cYcUII3-VLsPsEHBpAAoiesPGIsmpw8kxFCeHwaOsPbraWCvJsCPi5eBgA1LV-EDSs-IK1_NQWbtZp0zQ9PBU_2xmx-nrEONl-wApUuzJ_fM3u9PI5KtCD84pRDH-c8Ttp9h"/>
+    <hyperlink ref="O18" r:id="rId50" display="https://octopart.com/opatz8j6/a1?t=4Z8yQeECmR4C_z5gZdYgUOSOHyk6lk_OfTENDZKAFXPT2tQGZiBsfNSIX7Obg_bNUM-M-P50rK5grVCpKdHOUirXoulna9sx1Zng_TssD5fGRSWHYW2nKx897nAhAn6sw-FFfzc26gxquiGhOEwj5hgp9aZFiN3P6l4AgSlLpOX8SbysAIrzoJzD7q-RTbDa4PCz5SGMuPeCVEz_6OYZTPZzg8BQ9qfO_AhS-1F28C7SdgRZHm19DLRwOSi1jSLYrTB3SvrmW-6THINXU8maj_s4"/>
+    <hyperlink ref="G19" r:id="rId51" display="DigiKey 160-1646-1-ND"/>
+    <hyperlink ref="H19" r:id="rId52" display="https://octopart.com/opatz8j6/a1?t=fzi2Mzy-EcZOdKC8ToF-PnqDMIsThTuC_iNzvBIBhBwifxpB6xcIPJ99q6uUpk0WtwTozeQ_XXufEFVJpKTEYVWriA_DkUl4mjfmRjN61EQJ-axdrFHdNvBJk6Zlr1m7ypSz02jB49M4ItVkVmVCxpbpSCIEcsXTVivjGhgIjWNGGjrkZxY67HFO_1hE1jXGOXUcxRSOStRTrhsLjRE0UmfcqCWO-Y_nZglSiQQpXdsGUEPfLn0g0MMO-0P4yTS9EFiqJL7NOHfPFpxy3ZPblW0"/>
+    <hyperlink ref="O19" r:id="rId53" display="https://octopart.com/opatz8j6/a1?t=-RJoa4vc2RNfxVMeTcMfx0QkVbhyUP4VBt6N5E_Pfv9v8iH9fNAG3yWuq3XXXTcYpR7yIeCajqoVfDldw8qNSPX4cMRlu8HHcPlo5uFFV4sbOeoOKudSD3I-eXuedEF8v9Hg5ieDrANhIulAghOZwwMfycBsW5xUCjOPCwRBQ9-S1YV3RN2PcXEZ63vpzSaajD-DOYuz9h6WcOIWyhBRYKABJoWuszE3iLAxdeEd7uKQNw_-eMUZX2Yh8YtJ3sIQNILtILe0bXboIZuShauCyVh8FA"/>
+    <hyperlink ref="G20" r:id="rId54" display="DigiKey 160-1433-1-ND"/>
+    <hyperlink ref="H20" r:id="rId55" display="https://octopart.com/opatz8j6/a1?t=JGMy1S1qxhcoLmPEALYDjxyIdX_DbFoXkTvyOq9BaNCLl_sSGPFbrw2toMYAd5_LtMgJjSkf2WRqwdc-QmJL1Kz2LttTJSCszc3dSnTSP_QbmTSr2GEZJkewN8nOmmFFhsgQ57t0i5Fsp0jMGUsNv2Fyegb_uNT2QjsZp3OlTTqXnO14KoZCk2dqIW1hlCSvuD4TKoucYi4Ap2IzUNiFVqhtoVdHYTZr9lB5EipVCwEtJegnegx5A71sv1QkslwEJ6x75PYVGJ2Hg_bx_Qjsf1mX"/>
+    <hyperlink ref="O20" r:id="rId56" display="https://octopart.com/opatz8j6/a1?t=Pu5jrhmsrlcz1codkQWlwt4Ssq1b5ZrTqGMRyLwKgJYehpc-3V6dWg_vcHzjmOzcT6SK6qHu4LgKq0PsKTduK3doJ1In2XhDwYDdv6-kA1isCGopIG5kFpg998tLnwLHByFCC4P8x-FtipurXGxqzWFS_Lo_qwUhcPs2dHNVlYbl-Dn_dIfOHhlPeSIFCb9ma1LlCF71ft8zp98-NpC7c4O_iVfu24VQpjNrcCaamGOqk1FQJQ67CW9bZ-kEX4rLrRWoWiCl2OljFd8qMPdEIY9S"/>
+    <hyperlink ref="G21" r:id="rId57" display="DigiKey 160-1446-1-ND"/>
+    <hyperlink ref="H21" r:id="rId58" display="https://octopart.com/opatz8j6/a1?t=kaaMQ92alPC-mX1q_ZGaIAsByIP8IAfVOF5lfs1Gwz0GyYmFJT20LQAMnKWKqcGUapWpmUevE11u9QG_Zt4N2cbufJyxAvB_hsDDpU5GdGLFFg8aRELG6vSIw4g1DHyb8qui_X3JE7Kv6d53VYXTIy_-2KTTqX7lbZbfDj4tqDGt_OE8rh1i0AbCo1DB02YTOogqYvRjTzL2VLFEqIJRbWJeQVZqZoEVV0RLu4G_iBGxAbu_RG_sy1ftqtni0Kd1JnnE9Y7v-8f9h8jp0rGYD4Nv"/>
+    <hyperlink ref="O21" r:id="rId59" display="https://octopart.com/opatz8j6/a1?t=cyyzQSuNi4YznIxyw6TRFNKGbTXRzxC5ZcNPpuJin5xNBIlLu_K1X2mSfWW5oyud5GAn_As6fHTD8wbHCJVrDQF-E36eR2Id_0R_2GK_5RanCld-6-RYafY0R6NfILeaRRF_Utbd4vuZL75yVAXhDKEfHRA9GiLzRpMgVGq3gVOzlQzVGPTvpmtfF2YEEmTW8UUV-LoDEVplD3HgElEFgKCEC7t1XzKqI9-FjCyTC97Vt9K4G9hvG9zAnjnLuUvlz7929kVwiJJnGjjc9czGRiPR5A"/>
+    <hyperlink ref="G22" r:id="rId60" display="Mouser 833-BZT52C3V6S-TP"/>
+    <hyperlink ref="H22" r:id="rId61" display="https://octopart.com/opatz8j6/a1?t=YakmmgQZ2cuLiGXF1toII5G-G0v2IC_yywHbJZXniYUXIqRI1pg1zDMcbJzyC-VlZDZq-PiD0vZtOyvd0GoCvodi20gSinDFcOredtVYyqfsOWUFuYkcVN4zsKS1pb52V9Yi_7dAQDXMCVfh8uclms78nVtGhlvVPQwzg8BAeZe401KkCHuP_SFDsfiYs_sUmkdENTloxHu1eWAtEuzBRmWoBq9jZvVpkWL2xyZpQRVvIwtOPF0Nv0kZRIN7SgNCqS67y40Ju9i1nFcEdWCemVpgHoU5"/>
+    <hyperlink ref="O22" r:id="rId62" display="https://octopart.com/opatz8j6/a1?t=rJU4KNO3Q3bWDrLtrdbN968lcP8E3RZTfC_NGme9BH7yuYQHhYqU4D4zDFsqxncamqoc1JZYRLx4s5sJVvDh1c1VKcQBLXLopH3Ntis1evMMNY4dAz8LsCUjT19VmuwoudXo7loyMJ40aKYjgvLueuRmiB3hqxSv4RHIOuBywIu-csZDKFlAZ1_-CZu4_MaClUtCqkWprZQIQeL7JhVYmzcADqqi-QcXjsBewka6lNCNkWv4FS9IZ7mM9oRIWRONU7UKajIlO2pRYGYDLoG1U_6L_L4"/>
+    <hyperlink ref="G23" r:id="rId63" display="Mouser 520-2333-250-BNT"/>
+    <hyperlink ref="H23" r:id="rId64" display="https://octopart.com/opatz8j6/a1?t=E4sWF5WTw_lHLWSvAVLaNAzKgMSFqkzfmQrkXIOW4kTxYnGKh2ZcF4ED_wLkfNcr93Kjaubh3KIh3s9EdYT06RTbiQizg8ofICyxXgW7HQVLL018MxC8gDd4Myz6-tGLEpoRIxErrqSp4oiyqcbaQ8dqXf3EokFkoDSr4WYYXQQy5cv7HIvouadDMuti871udI9ctuTZ0GyrJLdcb8xutvncf-fNAclQyur68eMM1zciKugdpPguxHoDCiaSw1pFNDZpOGJeQLWBOM-kCrYhtjk6C2Ld"/>
+    <hyperlink ref="O23" r:id="rId65" display="https://octopart.com/opatz8j6/a1?t=mSq67AvCLCLIiFe4k_bRHIapePBV2HDhPAm4LaNtFOF72rhQRyzqlti8__PtH9KK8gHew9QsPNRf_7ALYfodUfqVELOdP63fNnYypHeWGkEhvfwydE3pfK5TQyr5u-OprFnWh-wdFugvv060ndsIpXdoj-5rYiTw9jToj8XHACz5mGTcMv6zJg9Ru_JlSgEMZRTVQ5tdDQ2t-s5OnZF25NtDCUaDZsApjuwBbDkcuEGv2Pq6oiSFWHyqidSn07QrTkchI34YdqEJuxyo03moSlrT3XY"/>
+    <hyperlink ref="G24" r:id="rId66" display="Mouser 798-DF40C100DP0.4V51"/>
+    <hyperlink ref="H24" r:id="rId67" display="https://octopart.com/opatz8j6/a1?t=GSvJ3-ybhEUhXL10fULYrnPWV_7Rl3bYrTfgtmWkJ4xAvP9aa8qSRz6hJSncoZ9ilhxJA3ZeZOQlNbhnW0bZlEiG0ODLU_EHi5nRWcjB6x6AvqmkQt9j3_myTpSDb1-EcwyRACO6fIFarDlZ0hCz1k2_xVBAvFUmxeZCWMbiBtp2h2Gjd4uez4oxkNI5wUvHFUhPbJdA9gVJZhxAaA9ZEvc42QAoHDwrIkv1zm7qmc0VOc3b0K0jjBz2Pb4YGB-KT0ucUbNIipbvrrmt0ehtz7rPX7-p"/>
+    <hyperlink ref="O24" r:id="rId68" display="https://octopart.com/opatz8j6/a1?t=Ry70Y5V9Nd6czZK8G8TPxUgDHTBWSkR_T88WM3i1uDvJfLVmc5lS_9kK1TwfknuRdZDtpmxSBE_-VkwO9odNjJ8LsF6epH8ti4p1280ARI29IyfnJJoiWxeO7wrMfOIhJIcrDG6MZt5YVKd1YFjP6w2sEYUA02WpvX5_txM0cVrqNEqS4w6SUr-X-9v8fjT3TqB6PZGFt5H6KX6x6navWOhMYduSpMRKl2QDTyyO81ai4hQ5OxpnTHQnncamfZKXEx_utSsFolALnnfZ_O_MTJGkJic"/>
+    <hyperlink ref="G25" r:id="rId69" display="Newark 97AK4032"/>
+    <hyperlink ref="H25" r:id="rId70" display="https://octopart.com/opatz8j6/a1?t=zyTuPDsPiVdvT_SCqBQZ0B6NHSnl5OCWlpV24EwKKr4OHIzXTAk2rZRu-As877AQhllMacDwJzuUcY3GRedI7RhstkwCXEhmPQpbtEYUOop0qOMarB4fqIPrKPM9KCwAM2r66mjRbg1LpYoGD7hUmyVP2cCyCFaEVwSd85m-dADJen57fGROknXicn-PvyHewqqzVH8lv5Lr4a-c8QVePY-jTfOnQSq6DqJ21_f-Jcrcdba3fUH7Q8RL1sW2NaszEO6yMX9-T8G6GOmc5FtPQIoAzC4w"/>
+    <hyperlink ref="O25" r:id="rId71" display="https://octopart.com/opatz8j6/a1?t=97pBINGDxY-yariYHpmZbV0OICU1Pxd2KFbY5E5wC2NglJWadSQfg3Lya5BaodT-erXPVSKbdi6dVwiB8-HXa2raUUqdxMdgdRRVYneq3k4a7Z7anfcCVlNzVPKns1awdtd5owXXbX1S39jwZ-va2pWfU_E_1VBP3uXVoQoIJZFaMi2GTZIp6x8UEiYPdF-qoujbP_V20_AXNmYbZ1xsnQalyXG-havOrGkRwrQz3xqW1yDG4FG0k7ld0D63epRPZGyxbdoo2rfaaNXHPrjozPvdsw"/>
+    <hyperlink ref="G26" r:id="rId72" display="Arrow Electronics RT0402BRD0712K1L"/>
+    <hyperlink ref="H26" r:id="rId73" display="https://octopart.com/opatz8j6/a1?t=1A279XklIitwWJEvO4vF-b2TjjaQAIS6AU0t0aypY37HTGFEQzvMQ3NtSpkhVjfhO-jtiRYPY1mdDoEVi7T8pV_EdJVvRgMEVny1PhSkKG_rsXbBmyIeuaZtppH4764mC-oCGclnq55GOY4CYzhpW_iz313CaAbPcNLAe_ZpX_A0837gpOVmHu6XS7IRo19sggohrMoXRHN4zujGpacrKzwX944OBcil1gKG8FjgkW6W-DQuoKS4ogjNym0bQxTzU6LXCQ7PkvIzUCOKQqvjThu8uws"/>
+    <hyperlink ref="G27" r:id="rId74" display="Mouser 842-LFE5U12F6BG381C"/>
+    <hyperlink ref="H27" r:id="rId75" display="https://octopart.com/opatz8j6/a1?t=NHw_We2NIaQQdPF_BLRd_EhqFIxHdHUAyYfMPjIi2dFNNOl3_ZMWvMwBoVNw6cCMDtEIlwhQu5BKrR_pH0dqhBO8j_ZZiwwzby6Q9plcp6U3yssNoqk9c4FNrUGMd7nlraHFrX1MRke4RC-juci68_hKUdCKi5rBdULtVnJJEtDAUHXuuFRw2CtpRAeVCZ5tPuEoIBtHRHa2PMWeGknLC5WN7tdCA-dFDQCTY8uSo7Gtr5KN-g1oJ-Nu_zb8s88R3UFgxP3IF9QiAM-5NALq0e-7fVp2"/>
+    <hyperlink ref="O27" r:id="rId76" display="https://octopart.com/opatz8j6/a1?t=vi9R2ddUfYB0Z-DMAq1x_YBmTkYs8GNQAc5dgp1sGmgQbFw4MS-weogcc_MFmzV576dKqpglTSQJpUP5O_Wwd2ISQyV8fsupxcIDB8s0jbR6TXHmaKkgmqYre37OgByGT7c3fNeuRU1lYYaso3DtLeWQ_jz9IQzN34RWCeBiXbb793yMUV3F6ijxqVpCPCuH9ZEs29KeCO7lsQc_cpj7--Dtl8HWW1PQ3E6BCRVgEMCL-VJawjvvaadjugDdyZQyRQcwSHMdAjRSEvq2-U8kJ6wsWYI0"/>
+    <hyperlink ref="G28" r:id="rId77" display="Mouser 870-42S16160J6BLI"/>
+    <hyperlink ref="H28" r:id="rId78" display="https://octopart.com/opatz8j6/a1?t=TDow5Ec7EHeW3_9HjQt7dBbG1yhsK9_I67TrKz99ijrswy3WIYZcYVvBHiZOP2WbcoG_HEBKfPV_GmiqWeyoEE2BLYBOVTYa-F6XZfhY4gfJpfiSej74wQR76GZ3iJSlZelb7DALve8kAnkXedvbIfDTx65RXiU7QOQPZxcIH5rMfaQsGRnQg8WQPmjQ9Bl6UTf0LmMSwipVlqkklfq15UPLHvBuDiW4qPseVRaUyrN9-uSZj2sNr0fmEM4PJNUvU0nb142qqYbZYqup9Iw-kgcGbdui"/>
+    <hyperlink ref="O28" r:id="rId79" display="https://octopart.com/opatz8j6/a1?t=OiK2wmnOg7L0CXEN2X-hI5yq4KnG7p3CN0iC3psSIlx5Bu1-y6d8j4oaIbY393oWPxAxvKKaxCTiJyPwgdUoZ61T8tBQpI1b05PFkkNI4Y06YAjBXuHrOt9EFIAaQ-F8TvlfR9QrQVrYi0R4Yu15e4bEJvfXkUVG12Oq3Ah0BbyHSn-NGaOizoPg6SqcBVDJhlZWFDvbcbS3Ol9LHfQFCLPPvnQyAOM7DZDyrS3BbuCI6Tch__vUiuTTc3kKTl73_qu_aj4Nqf1QjEfq4LXnrtFCHPT1YQ"/>
+    <hyperlink ref="G29" r:id="rId80" display="Arrow Electronics IS25LP128F-JBLE"/>
+    <hyperlink ref="H29" r:id="rId81" display="https://octopart.com/opatz8j6/a1?t=3t6UbzS-NE1YVYInzkVwhuqwODyKnlVUnrXj_Dm6E3fGBif_s3yinz1_EDg_kroJQwO4cJvo1P1ZN8_Rzf_MGBpOIhtSpGv_vnUGa0SV1mhkoMkxdCm8ZTeI96kgalMqP6k90a_NVaPbpXB9moM5MnymPXVP-iSljijkTjzl7PGMFPtgVHCDTHciFmvRkUlaa4knpAGe5Q7wKZOBB7Xlylo9Ns-owcbkaJpk1ejUjgr0Th2kkDIsjwb_V_NfesCWltWS_zj9pw9JbXQ-m539hvHG78xG"/>
+    <hyperlink ref="O29" r:id="rId82" display="https://octopart.com/opatz8j6/a1?t=GHBxJ10kL47vjux6hTkOFHHUq0NqtCHDu7rOd5w34bWCYCKZoxOLcoDL9J3T_oKPQLCMWzqcLyIxt9zpz49i9bq4snbmZVtSHhM5Gom0kELIeg52ZOEv2bxlJHQ46CfZ4LFp5EataNJJAsb13uCmMRjvIYIlluJLI5VZhc8tQjLds2ivTA5kjVvc17cROC0J1gkQT4Xx5YcwSAqFg0b7uOtJolOiysLvvLyRIm-t-bTwqDZU3jLVEtNvbOSxiVWVWzZWbYHfMZa0C-fT5kTv2A4pQiGy"/>
+    <hyperlink ref="G30" r:id="rId83" display="Mouser 579-LAN8720AICPTRABC"/>
+    <hyperlink ref="H30" r:id="rId84" display="https://octopart.com/opatz8j6/a1?t=GEmbYKTbx4xn-BVBNFTRkEU_vMzSHrxyG_flue6nv0_DepKR45Z4hViW_-oqD_4UfL80Th61R2CMdCOfiwcztVc2TbHVdVFHSzoFBwCsyvO-MueXTq4w_WszmMdEWY-gwBPybLwMWGI21SRp26BMEVZZQb9d-fcrt3ydPGShXuZ0h3Yjo6nHKcGdcMWEIhUM84qmlMPUUFXx8Ie1JD7R5F75oc26YZSc-zoQo-4krW7e5u0YEcomtk-YMa7jdZC579zZHoYGZEVUzYu2HhcvqJ90olQ"/>
+    <hyperlink ref="O30" r:id="rId85" display="https://octopart.com/opatz8j6/a1?t=acaDbe9ReO2_lo3YTaa0JocVK9CjjgmA4ewAvDD210E2B3tfheiPFZcb6dYnFD75TdNBe33tHID6qz62H5iUFi_LrfTOs5l9TizaZLRIRjVJNr8fh6JzwEYYdxuOap-Silr-dpvMaYY1salofpP6mYXO3TFpO4-ViDEzYtUxsxHUdDLJTywQXkfa5mHxhe0mm2HD7HgWpK39o0pvn6kj-Rw1xYT1EblybDrFA-HKLJTyAw5Kx5C8V6OAOyn0znMveeIQResgIY-lyAjD_76oEn6IUnehTw"/>
+    <hyperlink ref="G31" r:id="rId86" display="Mouser 229-CVS-02TB"/>
+    <hyperlink ref="H31" r:id="rId87" display="https://octopart.com/opatz8j6/a1?t=e7COkKmvLUBCVBAhSWIP1P795VAuu92Mwe0bzyzUtm63aJ2dZMQYq9o0c6lQSnyLRx51gEDc1hgu-B4sZ8yu4imvVGAummUkfJCtHhV-G8VJ6HOU36DadUwmsitz1H8OxoIB_-10OyO2yDU9JbA9uNMoXxYyg1RuprQgd8hmLKdNyOmz-Z3tdgu5_mPtE2UzFfZc0ivOitCr15dvggkMkK6reJN0vjDHLK5S1j_q773Qe1ZRBhBMYSMxcxI1Gx23cesoTdqg04gPTTllXYKeH2cN1TxJzg"/>
+    <hyperlink ref="O31" r:id="rId88" display="https://octopart.com/opatz8j6/a1?t=MuoUORcf9wegHACEDiAx7DbMsTpjjE4DCgH7Pb_LmNdq-R7I1-NC0KJN0uzJsNFbyHP1n00BwkUeGqPQFKQjPkKqX_-G5Vun_9w6_x0jYYdQJWvZXtWzgVMgW5v7zuTMdhjrhZgJqMzYRdF50l_tNfGHa-M9gDY6J5WO4Y5RAG1IwdcSodFEgmnLnqnPlX-9PtMVr8Srk0pdYXNon6OMXm5TOe2XX-WFnw1mkkftLTyvLPtRpuPE8XfA4pjwh_gsxdUjbhzV85TLPw5cO1iZM2CZfxzZlw"/>
+    <hyperlink ref="G32" r:id="rId89" display="Arrow Electronics 10118192-0001LF"/>
+    <hyperlink ref="H32" r:id="rId90" display="https://octopart.com/opatz8j6/a1?t=xGwT-_wxm-xxaVjbOcuqPEqHxZnWOBl39WypdCzKioq7NwL2xFNZZi5uwBgfz4AE5IhXFPIZS4OETurpHl-HcYcDJsG6MEVWVoIPyKAQoMgUmnUg846rwDKUL3GVaWkgyKLbpGkQVWrV79JxHCWS0fYt21S3Oy--yvVM7KypJPfat2Xo7y4SqSRewX8rQtqrdOAyhWzUsoqJr-qw7IfCTsOHaieSzKzG5iuFqXIhn4izTcW25-Tl4rttqumF6zQrHT0oVX4OwOzOPs6-zlPwUWeMAhPJjQ"/>
+    <hyperlink ref="O32" r:id="rId91" display="https://octopart.com/opatz8j6/a1?t=UoF7ECcaEe_D_84vCdLpDp39F3UvENsUx_0xifbykmhoCd48kuAT5JTvKjdMzJzvIe_nwkmaxKsCJgnvo8sYMCxKPqNeHCrh7sfMbOCjXoTia2IZZzncSLPZ4yc0oClJhyIa8_L435oRc6GtCeQhY3cCRXAHEAtOI2MutEWKrLqAwYSCXcTNHzdlIOo8Cu7ws_DvloGIemNJaznqANEYapr6FJ92TM45Rh3sJfD33rpiDteTFDIvpoQgX-aUhHQnV-PMGj8AuziFAb7g6D92bIZYAfqptw"/>
+    <hyperlink ref="G33" r:id="rId92" display="Arrow Electronics AC0402JR-073K3L"/>
+    <hyperlink ref="H33" r:id="rId93" display="https://octopart.com/opatz8j6/a1?t=j748atneLsEWEhDK__DYCImV0I1d1jv-KvoVj-JMLP1UlAgFAP5RN4zjx0tgpmtAa_e_PmJKEIA7jJhNXVn7-yy2PaA20LJgMmx5mQXlllccNwWwkgGRObA3du1nhOqD38mtnRVELKaIeEmMwpGHvRUVrNdKSg1VtL2GwSK8UdzNiW2eManuz7IUCGXyMRjKxcTCSGZlUjOmbaoegKpThVUhhuqQttGrnI8YsR-SwScBC4bNjImvWoNG8ncXw-Bc6_Gu__xz5gpAKy55dEM1TRVOEENT"/>
+    <hyperlink ref="O33" r:id="rId94" display="https://octopart.com/opatz8j6/a1?t=kM2oQZCTN63woZ2J-R_QGI_mWWfcA3hYWb9XDJ8I5wjHKx9hWIhqzoKooSpm7Bhgmq3-gt2BFyFlkUa4_oMF6C6fOUAeZpMLvasPs8Xlufkss7xF8gpG46Sw0Q0L4QWxgiix8B8kFRnYgtQ5OT1eqQG7A8Ur7iWvme6VyvdCv-ohQ2pw1JazxCR7ikNz5BZmUEzxir0q5dSkiux6PbvTlkUkLE5-f8G8Hvog-R9ZkiBJcDOk7x5T6Khy43lVxg-6y5FB3oiD8Am_ZUkCpYY6LiBR2ks"/>
+    <hyperlink ref="G34" r:id="rId95" display="Mouser 603-AC0402JR-0718KL"/>
+    <hyperlink ref="H34" r:id="rId96" display="https://octopart.com/opatz8j6/a1?t=EbzFpn45QbztmSEVZdek2jFDL0yrs0RVmck3uHBzOFY5YRYiO56VZWBrkYjM9BIxRZ-hpK_lHlS_6Vn4iaI-lmCRbDaYeFW-fLBx5GAdnU9zE1hCyv8Wt4LJLX1CfSZSPUb6Y_9YUpR_p-HjKzewLMyQrRxO1qLk8oA3dxHSq6xnPQD3QvQdDZ9dyVqDUDetCLHwboEMLZ-NglFWMA_DGGSrd9qFMPLwC6duMjlppRBrtRmSX-E1PWS3KacoYl9UQvh3Kj-66jLlTbfRhpKOppeOeyOj"/>
+    <hyperlink ref="O34" r:id="rId97" display="https://octopart.com/opatz8j6/a1?t=lHsPPhSDmyVQoXi-roIdbx_1I56VikOBKPyjcG6ZI-9yotLkLT-j4LEoIXYhDshoGZqrd75vw6HTXzRynSKU0aSBszSB22KfYwDiCJF5NJ-6E-rcYvWtEtUE4iVa8-Q0BwfQV0s-ktzWnhe_kjk4sqACoecU-jKmixqP1SBJyc2CplydhuldmLZYJEhIzDt76D1V0gSBoKlCpt9ZhwlL_RTx5j5X2TxDTSjlXuGgKWlHjEAHTOAARhfMjLZ9SKM9hWQNgr49bYni6UZJjRSAWW-Dzpk"/>
+    <hyperlink ref="G35" r:id="rId98" display="Newark 59AK3056"/>
+    <hyperlink ref="H35" r:id="rId99" display="https://octopart.com/opatz8j6/a1?t=I-hWLsLPiOj1_DhHYBdF88CiYoErg-DEEuiPkOPYYqhYhG4MQjIY3RwQTjme3M5YoZXbtIjqEtZ61SZZJve1TRUfidCDeSRBsFxzLnfONo_uWhEzfs5CrholaJMbMsVY7zVxGS0pDUKexLQTg8SQuqKVobqHKnmO9Om7gqfHxqUC74yaaAr2OstH7Y5eKvhKtzzhs97-yZ3aEE4J7Hca1-ZCujWKfPDp-aHX_sHRTbrP5h07knU3b_4DxbmbLsNF0w6d-j-dNYdWP8VgM3TmG0zVNq5E"/>
+    <hyperlink ref="O35" r:id="rId100" display="https://octopart.com/opatz8j6/a1?t=rPjJZ6CqLGe9iLMXm09Bm4eU2FEsBa5dly-XC1deN6qKsMyPeiDrr9HNubztWp66pl-9mKGy1VRNuTFNQS7UE2Hkff3ZUmTKGhQo8GpL_kM9PkodW7DB9siYqTC4kaJ8LeUL2SYXWvZqkIVeXiNRJzTgikMUeWPDMI7E-zZEUN-iHOI_2xXHYSHYs3MIrs8aTkOoAH2qzT1NFeKAwqv5rJtGjjHrSUsM7zDySj1MehAmWlC0u2zBIOSCwIFd-qSxR9JjHYlebCbgCVK-xWWcXwHDfBFR"/>
+    <hyperlink ref="G36" r:id="rId101" display="Newark 49AK6954"/>
+    <hyperlink ref="H36" r:id="rId102" display="https://octopart.com/opatz8j6/a1?t=MQuAwuMoCM9oQEU2Wwrv6S0jntIdg2z5ipw7ciYWmHy8eWhSKdospqoUzswygQmf7DcgVpIzjibeJg0-gP0nrgR8RMxGMaqCEzqi-qlYUYfB3vETjakmA_RdW_7r0aCS55rBE1IpTla6h2BEj-hbEZszuIm6zlObTCkOBAODeGIUYdDdNDB-yPKM43ELiRps9AgraF6UGzAyEn3SP6m4cd5d_wCtanmq0KBA0eD6BhLFrcr2EESQ0dEWg4a4vrFujNfcvhHapSbc37zi7pf9BOs-zaZn"/>
+    <hyperlink ref="O36" r:id="rId103" display="https://octopart.com/opatz8j6/a1?t=9NjSGnyaE2OiXrOCtPJMuyk0xKFm82ZrRjkULZpQmdRv775FwxilwGCUZpnlQWU1PN5g4dwlwfiJPmbgc58mhlI092ChV7NUzrfSF2779zM7t2xHqJ2Fsbj6-WvOTynVKOgWGk-T2mhOOOuCP5z6hyBvhp6alDDCxlQHQkkNBKdny2CPzlbYHzPtyQJHazfYb4rxnZYFPuGFm9z3xC7EjnS60jiKz2PIUxJHi_2CjRrkZ4EPgrqJ-2Cj81AASuZqEVq5lFyaFAnoU9ywNNZ1POegS3Ed"/>
+    <hyperlink ref="G37" r:id="rId104" display="Mouser 81-BLM18PG121SN1D"/>
+    <hyperlink ref="H37" r:id="rId105" display="https://octopart.com/opatz8j6/a1?t=1qH2d21Tvjz5pRpJhyud69BzvSOdXGWB9wG-cGwonWlZxYL_ZKeUv7C9IW7pXDEV6iwk2onNSsQfMbQ-SIRKhqt0tqeUUPYtbxfCHORahdoJvSsvOXB8dZBVdmABDgDeD4IiWH2_TmQWJFUrN_SsaMlT2im6bowHyIhyXbbNNXgIjt-V5V7dLyArDejZjbR3Ki3uk4m5Peyd43hDxfqWj2Fz38XvrdM7z78dK0pxtgOmSjSTAcBOD_XW1tudS1l9OmHfhXT3pEgWC3hd-czXF3-Gpw"/>
+    <hyperlink ref="G38" r:id="rId106" display="Arrow Electronics GRM155R71H471KA01J"/>
+    <hyperlink ref="H38" r:id="rId107" display="https://octopart.com/opatz8j6/a1?t=f0Ukf-STZBo7bhooAROoCLCltSPN55tWcKI4ZS6ZZ5om3Cy96Hvd3irAEMHgo269mQQydb5_pV59DEb4m8cCPgV_xK1ieexkguHI6Zs1eYiJGs-pHSw09-quPcqb3gxyO2ZL450lKOdei2voUNTsDdsBxYK1r_H1qBR-ZCcF8ldFcook2ypYIBDJY290lZTG8s2DEY-K0QI7TWsKVSr3UUhOpG_E7-Fx9PiTXwxWN1Am8-LmoLu0fjjY0H29buWd2-eCPA08oKOfE40MeerMWi9onZs"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
